--- a/Pacing_Dates_Master.xlsx
+++ b/Pacing_Dates_Master.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\github\GCI\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:9_{8D15E081-92DE-4E0A-94BB-F1C9038DB1D6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4EA7F61A-2AFF-4276-981A-EDCBB40F2B7A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="23260" windowHeight="14860" xr2:uid="{FBBB3D98-F469-4D19-87FE-9B4134E73E26}"/>
+    <workbookView xWindow="11430" yWindow="0" windowWidth="11700" windowHeight="14730" xr2:uid="{FBBB3D98-F469-4D19-87FE-9B4134E73E26}"/>
   </bookViews>
   <sheets>
     <sheet name="Pacing_Dates_Master" sheetId="1" r:id="rId1"/>
@@ -23,7 +23,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1045" uniqueCount="96">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1113" uniqueCount="108">
   <si>
     <t>SourceType</t>
   </si>
@@ -79,39 +79,18 @@
     <t>Computer Design Presentations</t>
   </si>
   <si>
-    <t>Reference day; classwork catch-up; Network Cable data</t>
-  </si>
-  <si>
     <t>Reference row</t>
   </si>
   <si>
-    <t>Reference day; classwork catch-up; Network Cable data; Cable practice and cord due</t>
-  </si>
-  <si>
-    <t>Teamwork</t>
-  </si>
-  <si>
-    <t>Base Camp (Computer Hardware)</t>
-  </si>
-  <si>
     <t>None</t>
   </si>
   <si>
-    <t>Classwork catch-up; Network Cable data; Teamwork assignment due (all hardware classes)</t>
-  </si>
-  <si>
     <t>Powers Catholic High School</t>
   </si>
   <si>
     <t>Classwork Catch-up and Network Cable Data</t>
   </si>
   <si>
-    <t>Classwork catch-up; Network Cable data</t>
-  </si>
-  <si>
-    <t>Cable practice and cord due; Certification - Network Fundamentals due</t>
-  </si>
-  <si>
     <t>Lakeville High School; Swartz Creek Community Schools</t>
   </si>
   <si>
@@ -130,9 +109,6 @@
     <t>Helpdesk Lab - Computer Build</t>
   </si>
   <si>
-    <t>Computer build lab work session</t>
-  </si>
-  <si>
     <t>Computer build lab work session; Cable practice and cord due</t>
   </si>
   <si>
@@ -154,18 +130,12 @@
     <t>Helpdesk Lab - 3D Printing</t>
   </si>
   <si>
-    <t>1st session 5-day lab</t>
-  </si>
-  <si>
     <t>Beecher High School; Bentley Community Schools; Davison Community Schools; Lakeville High School</t>
   </si>
   <si>
     <t>Flushing Community Schools</t>
   </si>
   <si>
-    <t>2nd session 5-day lab</t>
-  </si>
-  <si>
     <t>Spring Advisory (No GCI)</t>
   </si>
   <si>
@@ -199,22 +169,7 @@
     <t>Problem Set Work Time</t>
   </si>
   <si>
-    <t>Reference day; daily problem set work time</t>
-  </si>
-  <si>
-    <t>Problem Set Due Date</t>
-  </si>
-  <si>
-    <t>Session 1: Problem Set 7 due; Session 2: Problem Set 6 due</t>
-  </si>
-  <si>
     <t>Base Camp (1st and 3rd session Computer Science)</t>
-  </si>
-  <si>
-    <t>Daily problem set work time until due date; Teamwork assignment due (1st session)</t>
-  </si>
-  <si>
-    <t>Daily problem set work time until due date</t>
   </si>
   <si>
     <t>Forensic Case 1: Logs</t>
@@ -299,9 +254,6 @@
     <t>Classwork Catch-up and Network Cable Data Due</t>
   </si>
   <si>
-    <t>Teamwork Assignment, Computer Design Presentations</t>
-  </si>
-  <si>
     <t>Teamwork Assignment, Problem Set Work Time</t>
   </si>
   <si>
@@ -312,13 +264,101 @@
   </si>
   <si>
     <t>Virtual Assignment</t>
+  </si>
+  <si>
+    <t>Certification - Network Fundamentals 
+Digital Forensics
+Cable practice and cord due;</t>
+  </si>
+  <si>
+    <t>Computer Design Presentations
+Cable practice and cord due</t>
+  </si>
+  <si>
+    <t>Teamwork Assignment, 
+Computer Design Presentations</t>
+  </si>
+  <si>
+    <t>Evolution of Technology</t>
+  </si>
+  <si>
+    <t>Operating Systems Security</t>
+  </si>
+  <si>
+    <t>Network Design</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Networking Services</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Build and Secure a Network</t>
+  </si>
+  <si>
+    <t>Lab: Windows Networking</t>
+  </si>
+  <si>
+    <t>Lab: Network Protocols</t>
+  </si>
+  <si>
+    <t>Lab: Setting up Remote Access</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Networking Infrastructure Quiz</t>
+  </si>
+  <si>
+    <t>Project: The Inside Scoop on LANs</t>
+  </si>
+  <si>
+    <t>Helpdesk lab - TBD</t>
+  </si>
+  <si>
+    <t>Identifying Risks</t>
+  </si>
+  <si>
+    <t>Assessing Risks</t>
+  </si>
+  <si>
+    <t>Risk Response</t>
+  </si>
+  <si>
+    <t>Penetration Testing</t>
+  </si>
+  <si>
+    <t>Risk Management Quiz</t>
+  </si>
+  <si>
+    <t>Problem Set 7 Due Date</t>
+  </si>
+  <si>
+    <t>Problem Set 6 Due Date</t>
+  </si>
+  <si>
+    <t>Problem set 8 Due</t>
+  </si>
+  <si>
+    <t>Problem Set 7 Due</t>
+  </si>
+  <si>
+    <t>CS50 Final Project</t>
+  </si>
+  <si>
+    <t>Problem Set 8 Due</t>
+  </si>
+  <si>
+    <t>Problem Set Work time</t>
+  </si>
+  <si>
+    <t>Catchup/Brain break</t>
+  </si>
+  <si>
+    <t>CS50 Final Project Presentation</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="18" x14ac:knownFonts="1">
+  <fonts count="20" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -452,6 +492,18 @@
       <name val="Aptos Narrow"/>
       <family val="2"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="8"/>
+      <color rgb="FF555555"/>
+      <name val="Arial"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="8"/>
+      <color rgb="FF555555"/>
+      <name val="Arial"/>
+      <family val="2"/>
     </font>
   </fonts>
   <fills count="33">
@@ -795,12 +847,18 @@
     <xf numFmtId="0" fontId="1" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="1" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="7">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="42">
     <cellStyle name="20% - Accent1" xfId="19" builtinId="30" customBuiltin="1"/>
@@ -1313,14 +1371,11 @@
       <c r="E8" t="s">
         <v>17</v>
       </c>
-      <c r="F8" t="s">
+      <c r="G8" t="s">
         <v>18</v>
       </c>
-      <c r="G8" t="s">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="9" spans="1:8" x14ac:dyDescent="0.35">
+    </row>
+    <row r="9" spans="1:8" ht="29" x14ac:dyDescent="0.35">
       <c r="A9" t="s">
         <v>15</v>
       </c>
@@ -1330,17 +1385,14 @@
       <c r="C9" s="1">
         <v>46087</v>
       </c>
-      <c r="D9" t="s">
-        <v>17</v>
+      <c r="D9" s="2" t="s">
+        <v>81</v>
       </c>
       <c r="E9" t="s">
         <v>17</v>
       </c>
-      <c r="F9" t="s">
-        <v>20</v>
-      </c>
       <c r="G9" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
     </row>
     <row r="10" spans="1:8" x14ac:dyDescent="0.35">
@@ -1354,19 +1406,16 @@
         <v>46090</v>
       </c>
       <c r="D10" t="s">
-        <v>21</v>
+        <v>77</v>
       </c>
       <c r="E10" t="s">
-        <v>21</v>
-      </c>
-      <c r="F10" t="s">
-        <v>22</v>
+        <v>77</v>
       </c>
       <c r="G10" t="s">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="11" spans="1:8" x14ac:dyDescent="0.35">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="11" spans="1:8" ht="29" x14ac:dyDescent="0.35">
       <c r="A11" t="s">
         <v>15</v>
       </c>
@@ -1376,17 +1425,14 @@
       <c r="C11" s="1">
         <v>46091</v>
       </c>
-      <c r="D11" t="s">
-        <v>91</v>
-      </c>
-      <c r="E11" t="s">
-        <v>91</v>
-      </c>
-      <c r="F11" t="s">
-        <v>24</v>
+      <c r="D11" s="2" t="s">
+        <v>82</v>
+      </c>
+      <c r="E11" s="2" t="s">
+        <v>82</v>
       </c>
       <c r="G11" t="s">
-        <v>25</v>
+        <v>20</v>
       </c>
     </row>
     <row r="12" spans="1:8" x14ac:dyDescent="0.35">
@@ -1400,16 +1446,13 @@
         <v>46092</v>
       </c>
       <c r="D12" t="s">
-        <v>26</v>
+        <v>21</v>
       </c>
       <c r="E12" t="s">
-        <v>90</v>
-      </c>
-      <c r="F12" t="s">
-        <v>27</v>
+        <v>75</v>
       </c>
       <c r="G12" t="s">
-        <v>23</v>
+        <v>19</v>
       </c>
     </row>
     <row r="13" spans="1:8" x14ac:dyDescent="0.35">
@@ -1428,14 +1471,11 @@
       <c r="E13" t="s">
         <v>17</v>
       </c>
-      <c r="F13" t="s">
-        <v>27</v>
-      </c>
       <c r="G13" t="s">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="14" spans="1:8" ht="29" x14ac:dyDescent="0.35">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="14" spans="1:8" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A14" t="s">
         <v>15</v>
       </c>
@@ -1446,16 +1486,13 @@
         <v>46094</v>
       </c>
       <c r="D14" s="2" t="s">
-        <v>86</v>
+        <v>80</v>
       </c>
       <c r="E14" s="2" t="s">
-        <v>86</v>
-      </c>
-      <c r="F14" t="s">
-        <v>28</v>
+        <v>71</v>
       </c>
       <c r="G14" t="s">
-        <v>29</v>
+        <v>22</v>
       </c>
     </row>
     <row r="15" spans="1:8" x14ac:dyDescent="0.35">
@@ -1469,16 +1506,16 @@
         <v>46097</v>
       </c>
       <c r="D15" t="s">
-        <v>64</v>
+        <v>49</v>
       </c>
       <c r="E15" t="s">
-        <v>64</v>
+        <v>49</v>
       </c>
       <c r="F15" t="s">
-        <v>30</v>
+        <v>23</v>
       </c>
       <c r="G15" t="s">
-        <v>31</v>
+        <v>24</v>
       </c>
     </row>
     <row r="16" spans="1:8" x14ac:dyDescent="0.35">
@@ -1492,13 +1529,13 @@
         <v>46098</v>
       </c>
       <c r="D16" t="s">
-        <v>65</v>
+        <v>50</v>
       </c>
       <c r="E16" t="s">
-        <v>65</v>
+        <v>50</v>
       </c>
       <c r="G16" t="s">
-        <v>31</v>
+        <v>24</v>
       </c>
     </row>
     <row r="17" spans="1:7" x14ac:dyDescent="0.35">
@@ -1512,16 +1549,16 @@
         <v>46099</v>
       </c>
       <c r="D17" t="s">
-        <v>66</v>
+        <v>51</v>
       </c>
       <c r="E17" t="s">
-        <v>66</v>
+        <v>51</v>
       </c>
       <c r="F17" t="s">
-        <v>32</v>
+        <v>25</v>
       </c>
       <c r="G17" t="s">
-        <v>33</v>
+        <v>26</v>
       </c>
     </row>
     <row r="18" spans="1:7" x14ac:dyDescent="0.35">
@@ -1535,16 +1572,13 @@
         <v>46100</v>
       </c>
       <c r="D18" t="s">
-        <v>34</v>
+        <v>27</v>
       </c>
       <c r="E18" t="s">
-        <v>34</v>
-      </c>
-      <c r="F18" t="s">
-        <v>35</v>
+        <v>27</v>
       </c>
       <c r="G18" t="s">
-        <v>31</v>
+        <v>24</v>
       </c>
     </row>
     <row r="19" spans="1:7" x14ac:dyDescent="0.35">
@@ -1558,16 +1592,13 @@
         <v>46101</v>
       </c>
       <c r="D19" t="s">
-        <v>34</v>
+        <v>28</v>
       </c>
       <c r="E19" t="s">
-        <v>34</v>
-      </c>
-      <c r="F19" t="s">
-        <v>36</v>
+        <v>27</v>
       </c>
       <c r="G19" t="s">
-        <v>31</v>
+        <v>24</v>
       </c>
     </row>
     <row r="20" spans="1:7" x14ac:dyDescent="0.35">
@@ -1581,16 +1612,13 @@
         <v>46104</v>
       </c>
       <c r="D20" t="s">
-        <v>34</v>
+        <v>27</v>
       </c>
       <c r="E20" t="s">
-        <v>34</v>
-      </c>
-      <c r="F20" t="s">
-        <v>35</v>
+        <v>27</v>
       </c>
       <c r="G20" t="s">
-        <v>25</v>
+        <v>20</v>
       </c>
     </row>
     <row r="21" spans="1:7" x14ac:dyDescent="0.35">
@@ -1604,16 +1632,13 @@
         <v>46105</v>
       </c>
       <c r="D21" t="s">
-        <v>34</v>
+        <v>27</v>
       </c>
       <c r="E21" t="s">
-        <v>34</v>
-      </c>
-      <c r="F21" t="s">
-        <v>35</v>
+        <v>27</v>
       </c>
       <c r="G21" t="s">
-        <v>37</v>
+        <v>29</v>
       </c>
     </row>
     <row r="22" spans="1:7" x14ac:dyDescent="0.35">
@@ -1627,16 +1652,13 @@
         <v>46106</v>
       </c>
       <c r="D22" t="s">
-        <v>34</v>
+        <v>27</v>
       </c>
       <c r="E22" t="s">
-        <v>34</v>
-      </c>
-      <c r="F22" t="s">
-        <v>35</v>
+        <v>27</v>
       </c>
       <c r="G22" t="s">
-        <v>23</v>
+        <v>19</v>
       </c>
     </row>
     <row r="23" spans="1:7" x14ac:dyDescent="0.35">
@@ -1650,16 +1672,13 @@
         <v>46107</v>
       </c>
       <c r="D23" t="s">
-        <v>34</v>
+        <v>27</v>
       </c>
       <c r="E23" t="s">
-        <v>34</v>
-      </c>
-      <c r="F23" t="s">
-        <v>35</v>
+        <v>27</v>
       </c>
       <c r="G23" t="s">
-        <v>23</v>
+        <v>19</v>
       </c>
     </row>
     <row r="24" spans="1:7" x14ac:dyDescent="0.35">
@@ -1673,16 +1692,13 @@
         <v>46108</v>
       </c>
       <c r="D24" t="s">
-        <v>34</v>
+        <v>30</v>
       </c>
       <c r="E24" t="s">
-        <v>34</v>
-      </c>
-      <c r="F24" t="s">
-        <v>38</v>
+        <v>27</v>
       </c>
       <c r="G24" t="s">
-        <v>39</v>
+        <v>31</v>
       </c>
     </row>
     <row r="25" spans="1:7" x14ac:dyDescent="0.35">
@@ -1696,16 +1712,16 @@
         <v>46111</v>
       </c>
       <c r="D25" t="s">
-        <v>87</v>
+        <v>72</v>
       </c>
       <c r="E25" t="s">
-        <v>87</v>
+        <v>72</v>
       </c>
       <c r="F25" t="s">
-        <v>40</v>
+        <v>32</v>
       </c>
       <c r="G25" t="s">
-        <v>41</v>
+        <v>33</v>
       </c>
     </row>
     <row r="26" spans="1:7" x14ac:dyDescent="0.35">
@@ -1719,16 +1735,16 @@
         <v>46112</v>
       </c>
       <c r="D26" t="s">
-        <v>87</v>
+        <v>72</v>
       </c>
       <c r="E26" t="s">
-        <v>87</v>
+        <v>72</v>
       </c>
       <c r="F26" t="s">
-        <v>40</v>
+        <v>32</v>
       </c>
       <c r="G26" t="s">
-        <v>41</v>
+        <v>33</v>
       </c>
     </row>
     <row r="27" spans="1:7" x14ac:dyDescent="0.35">
@@ -1742,16 +1758,16 @@
         <v>46113</v>
       </c>
       <c r="D27" t="s">
-        <v>87</v>
+        <v>72</v>
       </c>
       <c r="E27" t="s">
-        <v>87</v>
+        <v>72</v>
       </c>
       <c r="F27" t="s">
-        <v>40</v>
+        <v>32</v>
       </c>
       <c r="G27" t="s">
-        <v>41</v>
+        <v>33</v>
       </c>
     </row>
     <row r="28" spans="1:7" x14ac:dyDescent="0.35">
@@ -1765,16 +1781,16 @@
         <v>46114</v>
       </c>
       <c r="D28" t="s">
-        <v>87</v>
+        <v>72</v>
       </c>
       <c r="E28" t="s">
-        <v>87</v>
+        <v>72</v>
       </c>
       <c r="F28" t="s">
-        <v>40</v>
+        <v>32</v>
       </c>
       <c r="G28" t="s">
-        <v>41</v>
+        <v>33</v>
       </c>
     </row>
     <row r="29" spans="1:7" x14ac:dyDescent="0.35">
@@ -1788,16 +1804,16 @@
         <v>46115</v>
       </c>
       <c r="D29" t="s">
-        <v>87</v>
+        <v>72</v>
       </c>
       <c r="E29" t="s">
-        <v>87</v>
+        <v>72</v>
       </c>
       <c r="F29" t="s">
-        <v>40</v>
+        <v>32</v>
       </c>
       <c r="G29" t="s">
-        <v>41</v>
+        <v>33</v>
       </c>
     </row>
     <row r="30" spans="1:7" x14ac:dyDescent="0.35">
@@ -1811,16 +1827,13 @@
         <v>46118</v>
       </c>
       <c r="D30" t="s">
-        <v>42</v>
+        <v>34</v>
       </c>
       <c r="E30" t="s">
-        <v>68</v>
-      </c>
-      <c r="F30" t="s">
-        <v>43</v>
+        <v>53</v>
       </c>
       <c r="G30" t="s">
-        <v>44</v>
+        <v>35</v>
       </c>
     </row>
     <row r="31" spans="1:7" x14ac:dyDescent="0.35">
@@ -1834,16 +1847,13 @@
         <v>46119</v>
       </c>
       <c r="D31" t="s">
-        <v>42</v>
+        <v>34</v>
       </c>
       <c r="E31" t="s">
-        <v>69</v>
-      </c>
-      <c r="F31" t="s">
-        <v>43</v>
+        <v>54</v>
       </c>
       <c r="G31" t="s">
-        <v>23</v>
+        <v>19</v>
       </c>
     </row>
     <row r="32" spans="1:7" x14ac:dyDescent="0.35">
@@ -1857,16 +1867,13 @@
         <v>46120</v>
       </c>
       <c r="D32" t="s">
-        <v>42</v>
+        <v>34</v>
       </c>
       <c r="E32" t="s">
-        <v>70</v>
-      </c>
-      <c r="F32" t="s">
-        <v>43</v>
+        <v>55</v>
       </c>
       <c r="G32" t="s">
-        <v>45</v>
+        <v>36</v>
       </c>
     </row>
     <row r="33" spans="1:7" x14ac:dyDescent="0.35">
@@ -1880,16 +1887,13 @@
         <v>46121</v>
       </c>
       <c r="D33" t="s">
-        <v>42</v>
+        <v>34</v>
       </c>
       <c r="E33" t="s">
-        <v>71</v>
-      </c>
-      <c r="F33" t="s">
-        <v>43</v>
+        <v>56</v>
       </c>
       <c r="G33" t="s">
-        <v>23</v>
+        <v>19</v>
       </c>
     </row>
     <row r="34" spans="1:7" x14ac:dyDescent="0.35">
@@ -1903,16 +1907,13 @@
         <v>46122</v>
       </c>
       <c r="D34" t="s">
-        <v>42</v>
+        <v>34</v>
       </c>
       <c r="E34" t="s">
-        <v>72</v>
-      </c>
-      <c r="F34" t="s">
-        <v>43</v>
+        <v>57</v>
       </c>
       <c r="G34" t="s">
-        <v>23</v>
+        <v>19</v>
       </c>
     </row>
     <row r="35" spans="1:7" x14ac:dyDescent="0.35">
@@ -1926,16 +1927,13 @@
         <v>46125</v>
       </c>
       <c r="D35" t="s">
-        <v>68</v>
+        <v>53</v>
       </c>
       <c r="E35" t="s">
-        <v>42</v>
-      </c>
-      <c r="F35" t="s">
-        <v>46</v>
+        <v>34</v>
       </c>
       <c r="G35" t="s">
-        <v>23</v>
+        <v>19</v>
       </c>
     </row>
     <row r="36" spans="1:7" x14ac:dyDescent="0.35">
@@ -1949,16 +1947,13 @@
         <v>46126</v>
       </c>
       <c r="D36" t="s">
-        <v>69</v>
+        <v>54</v>
       </c>
       <c r="E36" t="s">
-        <v>42</v>
-      </c>
-      <c r="F36" t="s">
-        <v>46</v>
+        <v>34</v>
       </c>
       <c r="G36" t="s">
-        <v>23</v>
+        <v>19</v>
       </c>
     </row>
     <row r="37" spans="1:7" x14ac:dyDescent="0.35">
@@ -1972,16 +1967,13 @@
         <v>46127</v>
       </c>
       <c r="D37" t="s">
-        <v>70</v>
+        <v>55</v>
       </c>
       <c r="E37" t="s">
-        <v>42</v>
-      </c>
-      <c r="F37" t="s">
-        <v>46</v>
+        <v>34</v>
       </c>
       <c r="G37" t="s">
-        <v>23</v>
+        <v>19</v>
       </c>
     </row>
     <row r="38" spans="1:7" x14ac:dyDescent="0.35">
@@ -1995,16 +1987,16 @@
         <v>46128</v>
       </c>
       <c r="D38" t="s">
-        <v>89</v>
+        <v>74</v>
       </c>
       <c r="E38" t="s">
-        <v>89</v>
+        <v>74</v>
       </c>
       <c r="F38" t="s">
-        <v>47</v>
+        <v>37</v>
       </c>
       <c r="G38" t="s">
-        <v>23</v>
+        <v>19</v>
       </c>
     </row>
     <row r="39" spans="1:7" x14ac:dyDescent="0.35">
@@ -2018,16 +2010,16 @@
         <v>46129</v>
       </c>
       <c r="D39" t="s">
-        <v>88</v>
+        <v>73</v>
       </c>
       <c r="E39" t="s">
-        <v>88</v>
+        <v>73</v>
       </c>
       <c r="F39" t="s">
-        <v>48</v>
+        <v>38</v>
       </c>
       <c r="G39" t="s">
-        <v>49</v>
+        <v>39</v>
       </c>
     </row>
     <row r="40" spans="1:7" x14ac:dyDescent="0.35">
@@ -2041,16 +2033,16 @@
         <v>46132</v>
       </c>
       <c r="D40" t="s">
-        <v>71</v>
+        <v>56</v>
       </c>
       <c r="E40" t="s">
-        <v>42</v>
+        <v>34</v>
       </c>
       <c r="F40" t="s">
-        <v>50</v>
+        <v>40</v>
       </c>
       <c r="G40" t="s">
-        <v>23</v>
+        <v>19</v>
       </c>
     </row>
     <row r="41" spans="1:7" x14ac:dyDescent="0.35">
@@ -2064,16 +2056,16 @@
         <v>46133</v>
       </c>
       <c r="D41" t="s">
-        <v>72</v>
+        <v>57</v>
       </c>
       <c r="E41" t="s">
-        <v>42</v>
+        <v>34</v>
       </c>
       <c r="F41" t="s">
-        <v>51</v>
+        <v>41</v>
       </c>
       <c r="G41" t="s">
-        <v>23</v>
+        <v>19</v>
       </c>
     </row>
     <row r="42" spans="1:7" x14ac:dyDescent="0.35">
@@ -2086,8 +2078,14 @@
       <c r="C42" s="1">
         <v>46134</v>
       </c>
+      <c r="D42" t="s">
+        <v>52</v>
+      </c>
+      <c r="E42" t="s">
+        <v>52</v>
+      </c>
       <c r="G42" t="s">
-        <v>23</v>
+        <v>19</v>
       </c>
     </row>
     <row r="43" spans="1:7" x14ac:dyDescent="0.35">
@@ -2100,8 +2098,14 @@
       <c r="C43" s="1">
         <v>46135</v>
       </c>
+      <c r="D43" s="3" t="s">
+        <v>83</v>
+      </c>
+      <c r="E43" s="3" t="s">
+        <v>83</v>
+      </c>
       <c r="G43" t="s">
-        <v>23</v>
+        <v>19</v>
       </c>
     </row>
     <row r="44" spans="1:7" x14ac:dyDescent="0.35">
@@ -2114,8 +2118,14 @@
       <c r="C44" s="1">
         <v>46136</v>
       </c>
+      <c r="D44" s="4" t="s">
+        <v>84</v>
+      </c>
+      <c r="E44" s="4" t="s">
+        <v>84</v>
+      </c>
       <c r="G44" t="s">
-        <v>23</v>
+        <v>19</v>
       </c>
     </row>
     <row r="45" spans="1:7" x14ac:dyDescent="0.35">
@@ -2128,8 +2138,14 @@
       <c r="C45" s="1">
         <v>46139</v>
       </c>
+      <c r="D45" s="5" t="s">
+        <v>85</v>
+      </c>
+      <c r="E45" s="5" t="s">
+        <v>85</v>
+      </c>
       <c r="G45" t="s">
-        <v>23</v>
+        <v>19</v>
       </c>
     </row>
     <row r="46" spans="1:7" x14ac:dyDescent="0.35">
@@ -2142,8 +2158,14 @@
       <c r="C46" s="1">
         <v>46140</v>
       </c>
+      <c r="D46" s="6" t="s">
+        <v>86</v>
+      </c>
+      <c r="E46" s="6" t="s">
+        <v>86</v>
+      </c>
       <c r="G46" t="s">
-        <v>23</v>
+        <v>19</v>
       </c>
     </row>
     <row r="47" spans="1:7" x14ac:dyDescent="0.35">
@@ -2156,8 +2178,14 @@
       <c r="C47" s="1">
         <v>46141</v>
       </c>
+      <c r="D47" s="4" t="s">
+        <v>87</v>
+      </c>
+      <c r="E47" s="4" t="s">
+        <v>87</v>
+      </c>
       <c r="G47" t="s">
-        <v>23</v>
+        <v>19</v>
       </c>
     </row>
     <row r="48" spans="1:7" x14ac:dyDescent="0.35">
@@ -2170,8 +2198,14 @@
       <c r="C48" s="1">
         <v>46142</v>
       </c>
+      <c r="D48" s="4" t="s">
+        <v>88</v>
+      </c>
+      <c r="E48" s="4" t="s">
+        <v>88</v>
+      </c>
       <c r="G48" t="s">
-        <v>23</v>
+        <v>19</v>
       </c>
     </row>
     <row r="49" spans="1:7" x14ac:dyDescent="0.35">
@@ -2184,8 +2218,14 @@
       <c r="C49" s="1">
         <v>46143</v>
       </c>
+      <c r="D49" s="4" t="s">
+        <v>89</v>
+      </c>
+      <c r="E49" s="4" t="s">
+        <v>89</v>
+      </c>
       <c r="G49" t="s">
-        <v>23</v>
+        <v>19</v>
       </c>
     </row>
     <row r="50" spans="1:7" x14ac:dyDescent="0.35">
@@ -2198,8 +2238,14 @@
       <c r="C50" s="1">
         <v>46146</v>
       </c>
+      <c r="D50" s="4" t="s">
+        <v>90</v>
+      </c>
+      <c r="E50" s="4" t="s">
+        <v>90</v>
+      </c>
       <c r="G50" t="s">
-        <v>23</v>
+        <v>19</v>
       </c>
     </row>
     <row r="51" spans="1:7" x14ac:dyDescent="0.35">
@@ -2212,8 +2258,14 @@
       <c r="C51" s="1">
         <v>46147</v>
       </c>
+      <c r="D51" s="4" t="s">
+        <v>91</v>
+      </c>
+      <c r="E51" s="4" t="s">
+        <v>91</v>
+      </c>
       <c r="G51" t="s">
-        <v>52</v>
+        <v>42</v>
       </c>
     </row>
     <row r="52" spans="1:7" x14ac:dyDescent="0.35">
@@ -2226,8 +2278,14 @@
       <c r="C52" s="1">
         <v>46148</v>
       </c>
+      <c r="D52" s="3" t="s">
+        <v>92</v>
+      </c>
+      <c r="E52" s="4" t="s">
+        <v>92</v>
+      </c>
       <c r="G52" t="s">
-        <v>23</v>
+        <v>19</v>
       </c>
     </row>
     <row r="53" spans="1:7" x14ac:dyDescent="0.35">
@@ -2240,8 +2298,14 @@
       <c r="C53" s="1">
         <v>46149</v>
       </c>
+      <c r="D53" s="3" t="s">
+        <v>92</v>
+      </c>
+      <c r="E53" s="4" t="s">
+        <v>92</v>
+      </c>
       <c r="G53" t="s">
-        <v>23</v>
+        <v>19</v>
       </c>
     </row>
     <row r="54" spans="1:7" x14ac:dyDescent="0.35">
@@ -2254,8 +2318,14 @@
       <c r="C54" s="1">
         <v>46150</v>
       </c>
+      <c r="D54" s="3" t="s">
+        <v>92</v>
+      </c>
+      <c r="E54" s="4" t="s">
+        <v>92</v>
+      </c>
       <c r="G54" t="s">
-        <v>23</v>
+        <v>19</v>
       </c>
     </row>
     <row r="55" spans="1:7" x14ac:dyDescent="0.35">
@@ -2268,8 +2338,14 @@
       <c r="C55" s="1">
         <v>46153</v>
       </c>
+      <c r="D55" s="3" t="s">
+        <v>93</v>
+      </c>
+      <c r="E55" s="3" t="s">
+        <v>93</v>
+      </c>
       <c r="G55" t="s">
-        <v>23</v>
+        <v>19</v>
       </c>
     </row>
     <row r="56" spans="1:7" x14ac:dyDescent="0.35">
@@ -2282,8 +2358,14 @@
       <c r="C56" s="1">
         <v>46154</v>
       </c>
+      <c r="D56" s="3" t="s">
+        <v>93</v>
+      </c>
+      <c r="E56" s="3" t="s">
+        <v>93</v>
+      </c>
       <c r="G56" t="s">
-        <v>23</v>
+        <v>19</v>
       </c>
     </row>
     <row r="57" spans="1:7" x14ac:dyDescent="0.35">
@@ -2296,8 +2378,14 @@
       <c r="C57" s="1">
         <v>46155</v>
       </c>
+      <c r="D57" s="3" t="s">
+        <v>93</v>
+      </c>
+      <c r="E57" s="3" t="s">
+        <v>93</v>
+      </c>
       <c r="G57" t="s">
-        <v>23</v>
+        <v>19</v>
       </c>
     </row>
     <row r="58" spans="1:7" x14ac:dyDescent="0.35">
@@ -2310,8 +2398,14 @@
       <c r="C58" s="1">
         <v>46156</v>
       </c>
+      <c r="D58" s="3" t="s">
+        <v>93</v>
+      </c>
+      <c r="E58" s="3" t="s">
+        <v>93</v>
+      </c>
       <c r="G58" t="s">
-        <v>23</v>
+        <v>19</v>
       </c>
     </row>
     <row r="59" spans="1:7" x14ac:dyDescent="0.35">
@@ -2324,8 +2418,14 @@
       <c r="C59" s="1">
         <v>46157</v>
       </c>
+      <c r="D59" s="3" t="s">
+        <v>93</v>
+      </c>
+      <c r="E59" s="3" t="s">
+        <v>93</v>
+      </c>
       <c r="G59" t="s">
-        <v>23</v>
+        <v>19</v>
       </c>
     </row>
     <row r="60" spans="1:7" x14ac:dyDescent="0.35">
@@ -2338,8 +2438,14 @@
       <c r="C60" s="1">
         <v>46160</v>
       </c>
+      <c r="D60" s="3" t="s">
+        <v>94</v>
+      </c>
+      <c r="E60" s="3" t="s">
+        <v>94</v>
+      </c>
       <c r="G60" t="s">
-        <v>23</v>
+        <v>19</v>
       </c>
     </row>
     <row r="61" spans="1:7" x14ac:dyDescent="0.35">
@@ -2352,8 +2458,14 @@
       <c r="C61" s="1">
         <v>46161</v>
       </c>
+      <c r="D61" s="3" t="s">
+        <v>95</v>
+      </c>
+      <c r="E61" s="3" t="s">
+        <v>95</v>
+      </c>
       <c r="G61" t="s">
-        <v>23</v>
+        <v>19</v>
       </c>
     </row>
     <row r="62" spans="1:7" x14ac:dyDescent="0.35">
@@ -2366,8 +2478,14 @@
       <c r="C62" s="1">
         <v>46162</v>
       </c>
+      <c r="D62" s="3" t="s">
+        <v>96</v>
+      </c>
+      <c r="E62" s="3" t="s">
+        <v>96</v>
+      </c>
       <c r="G62" t="s">
-        <v>23</v>
+        <v>19</v>
       </c>
     </row>
     <row r="63" spans="1:7" x14ac:dyDescent="0.35">
@@ -2380,8 +2498,14 @@
       <c r="C63" s="1">
         <v>46163</v>
       </c>
+      <c r="D63" s="3" t="s">
+        <v>97</v>
+      </c>
+      <c r="E63" s="3" t="s">
+        <v>97</v>
+      </c>
       <c r="G63" t="s">
-        <v>23</v>
+        <v>19</v>
       </c>
     </row>
     <row r="64" spans="1:7" x14ac:dyDescent="0.35">
@@ -2394,11 +2518,17 @@
       <c r="C64" s="1">
         <v>46164</v>
       </c>
+      <c r="D64" s="3" t="s">
+        <v>74</v>
+      </c>
+      <c r="E64" s="3" t="s">
+        <v>74</v>
+      </c>
       <c r="F64" t="s">
-        <v>53</v>
+        <v>43</v>
       </c>
       <c r="G64" t="s">
-        <v>23</v>
+        <v>19</v>
       </c>
     </row>
     <row r="65" spans="1:7" x14ac:dyDescent="0.35">
@@ -2411,11 +2541,17 @@
       <c r="C65" s="1">
         <v>46167</v>
       </c>
+      <c r="D65" s="3" t="s">
+        <v>74</v>
+      </c>
+      <c r="E65" s="3" t="s">
+        <v>74</v>
+      </c>
       <c r="F65" t="s">
-        <v>54</v>
+        <v>44</v>
       </c>
       <c r="G65" t="s">
-        <v>55</v>
+        <v>45</v>
       </c>
     </row>
     <row r="66" spans="1:7" x14ac:dyDescent="0.35">
@@ -2428,8 +2564,14 @@
       <c r="C66" s="1">
         <v>46168</v>
       </c>
+      <c r="D66" s="3" t="s">
+        <v>98</v>
+      </c>
+      <c r="E66" s="3" t="s">
+        <v>98</v>
+      </c>
       <c r="G66" t="s">
-        <v>23</v>
+        <v>19</v>
       </c>
     </row>
     <row r="67" spans="1:7" x14ac:dyDescent="0.35">
@@ -2442,8 +2584,14 @@
       <c r="C67" s="1">
         <v>46169</v>
       </c>
+      <c r="D67" s="3" t="s">
+        <v>93</v>
+      </c>
+      <c r="E67" s="3" t="s">
+        <v>93</v>
+      </c>
       <c r="G67" t="s">
-        <v>23</v>
+        <v>19</v>
       </c>
     </row>
     <row r="68" spans="1:7" x14ac:dyDescent="0.35">
@@ -2456,8 +2604,14 @@
       <c r="C68" s="1">
         <v>46170</v>
       </c>
+      <c r="D68" s="3" t="s">
+        <v>93</v>
+      </c>
+      <c r="E68" s="3" t="s">
+        <v>93</v>
+      </c>
       <c r="G68" t="s">
-        <v>23</v>
+        <v>19</v>
       </c>
     </row>
     <row r="69" spans="1:7" x14ac:dyDescent="0.35">
@@ -2470,8 +2624,14 @@
       <c r="C69" s="1">
         <v>46171</v>
       </c>
+      <c r="D69" s="3" t="s">
+        <v>93</v>
+      </c>
+      <c r="E69" s="3" t="s">
+        <v>93</v>
+      </c>
       <c r="G69" t="s">
-        <v>23</v>
+        <v>19</v>
       </c>
     </row>
     <row r="70" spans="1:7" x14ac:dyDescent="0.35">
@@ -2484,8 +2644,14 @@
       <c r="C70" s="1">
         <v>46174</v>
       </c>
+      <c r="D70" s="3" t="s">
+        <v>93</v>
+      </c>
+      <c r="E70" s="3" t="s">
+        <v>93</v>
+      </c>
       <c r="G70" t="s">
-        <v>23</v>
+        <v>19</v>
       </c>
     </row>
     <row r="71" spans="1:7" x14ac:dyDescent="0.35">
@@ -2498,8 +2664,14 @@
       <c r="C71" s="1">
         <v>46175</v>
       </c>
+      <c r="D71" s="3" t="s">
+        <v>93</v>
+      </c>
+      <c r="E71" s="3" t="s">
+        <v>93</v>
+      </c>
       <c r="G71" t="s">
-        <v>23</v>
+        <v>19</v>
       </c>
     </row>
     <row r="72" spans="1:7" x14ac:dyDescent="0.35">
@@ -2512,8 +2684,14 @@
       <c r="C72" s="1">
         <v>46176</v>
       </c>
+      <c r="D72" s="3" t="s">
+        <v>93</v>
+      </c>
+      <c r="E72" s="3" t="s">
+        <v>93</v>
+      </c>
       <c r="G72" t="s">
-        <v>23</v>
+        <v>19</v>
       </c>
     </row>
     <row r="73" spans="1:7" x14ac:dyDescent="0.35">
@@ -2526,8 +2704,14 @@
       <c r="C73" s="1">
         <v>46177</v>
       </c>
+      <c r="D73" s="3" t="s">
+        <v>93</v>
+      </c>
+      <c r="E73" s="3" t="s">
+        <v>93</v>
+      </c>
       <c r="G73" t="s">
-        <v>23</v>
+        <v>19</v>
       </c>
     </row>
     <row r="74" spans="1:7" x14ac:dyDescent="0.35">
@@ -2540,8 +2724,14 @@
       <c r="C74" s="1">
         <v>46178</v>
       </c>
+      <c r="D74" s="3" t="s">
+        <v>93</v>
+      </c>
+      <c r="E74" s="3" t="s">
+        <v>93</v>
+      </c>
       <c r="G74" t="s">
-        <v>23</v>
+        <v>19</v>
       </c>
     </row>
     <row r="75" spans="1:7" x14ac:dyDescent="0.35">
@@ -2554,8 +2744,14 @@
       <c r="C75" s="1">
         <v>46181</v>
       </c>
+      <c r="D75" s="3" t="s">
+        <v>93</v>
+      </c>
+      <c r="E75" s="3" t="s">
+        <v>93</v>
+      </c>
       <c r="G75" t="s">
-        <v>23</v>
+        <v>19</v>
       </c>
     </row>
     <row r="76" spans="1:7" x14ac:dyDescent="0.35">
@@ -2568,8 +2764,14 @@
       <c r="C76" s="1">
         <v>46182</v>
       </c>
+      <c r="D76" s="3" t="s">
+        <v>93</v>
+      </c>
+      <c r="E76" s="3" t="s">
+        <v>93</v>
+      </c>
       <c r="G76" t="s">
-        <v>23</v>
+        <v>19</v>
       </c>
     </row>
     <row r="77" spans="1:7" x14ac:dyDescent="0.35">
@@ -2577,22 +2779,19 @@
         <v>15</v>
       </c>
       <c r="B77" t="s">
-        <v>56</v>
+        <v>46</v>
       </c>
       <c r="C77" s="1">
         <v>46086</v>
       </c>
       <c r="D77" t="s">
-        <v>57</v>
+        <v>47</v>
       </c>
       <c r="E77" t="s">
-        <v>57</v>
-      </c>
-      <c r="F77" t="s">
-        <v>58</v>
+        <v>47</v>
       </c>
       <c r="G77" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
     </row>
     <row r="78" spans="1:7" x14ac:dyDescent="0.35">
@@ -2600,22 +2799,19 @@
         <v>15</v>
       </c>
       <c r="B78" t="s">
-        <v>56</v>
+        <v>46</v>
       </c>
       <c r="C78" s="1">
         <v>46087</v>
       </c>
       <c r="D78" t="s">
-        <v>59</v>
+        <v>99</v>
       </c>
       <c r="E78" t="s">
-        <v>59</v>
-      </c>
-      <c r="F78" t="s">
-        <v>60</v>
+        <v>100</v>
       </c>
       <c r="G78" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
     </row>
     <row r="79" spans="1:7" x14ac:dyDescent="0.35">
@@ -2623,19 +2819,19 @@
         <v>15</v>
       </c>
       <c r="B79" t="s">
-        <v>56</v>
+        <v>46</v>
       </c>
       <c r="C79" s="1">
         <v>46090</v>
       </c>
       <c r="D79" t="s">
-        <v>93</v>
+        <v>77</v>
       </c>
       <c r="F79" t="s">
-        <v>61</v>
+        <v>48</v>
       </c>
       <c r="G79" t="s">
-        <v>23</v>
+        <v>19</v>
       </c>
     </row>
     <row r="80" spans="1:7" x14ac:dyDescent="0.35">
@@ -2643,19 +2839,16 @@
         <v>15</v>
       </c>
       <c r="B80" t="s">
-        <v>56</v>
+        <v>46</v>
       </c>
       <c r="C80" s="1">
         <v>46091</v>
       </c>
       <c r="D80" t="s">
-        <v>92</v>
-      </c>
-      <c r="F80" t="s">
-        <v>62</v>
+        <v>76</v>
       </c>
       <c r="G80" t="s">
-        <v>25</v>
+        <v>20</v>
       </c>
     </row>
     <row r="81" spans="1:7" x14ac:dyDescent="0.35">
@@ -2663,22 +2856,19 @@
         <v>15</v>
       </c>
       <c r="B81" t="s">
-        <v>56</v>
+        <v>46</v>
       </c>
       <c r="C81" s="1">
         <v>46092</v>
       </c>
       <c r="D81" t="s">
-        <v>57</v>
+        <v>47</v>
       </c>
       <c r="E81" t="s">
-        <v>57</v>
-      </c>
-      <c r="F81" t="s">
-        <v>63</v>
+        <v>47</v>
       </c>
       <c r="G81" t="s">
-        <v>23</v>
+        <v>19</v>
       </c>
     </row>
     <row r="82" spans="1:7" x14ac:dyDescent="0.35">
@@ -2686,22 +2876,19 @@
         <v>15</v>
       </c>
       <c r="B82" t="s">
-        <v>56</v>
+        <v>46</v>
       </c>
       <c r="C82" s="1">
         <v>46093</v>
       </c>
       <c r="D82" t="s">
-        <v>57</v>
+        <v>47</v>
       </c>
       <c r="E82" t="s">
-        <v>57</v>
-      </c>
-      <c r="F82" t="s">
-        <v>63</v>
+        <v>47</v>
       </c>
       <c r="G82" t="s">
-        <v>23</v>
+        <v>19</v>
       </c>
     </row>
     <row r="83" spans="1:7" x14ac:dyDescent="0.35">
@@ -2709,13 +2896,19 @@
         <v>15</v>
       </c>
       <c r="B83" t="s">
-        <v>56</v>
+        <v>46</v>
       </c>
       <c r="C83" s="1">
         <v>46094</v>
       </c>
+      <c r="D83" t="s">
+        <v>101</v>
+      </c>
+      <c r="E83" t="s">
+        <v>102</v>
+      </c>
       <c r="G83" t="s">
-        <v>29</v>
+        <v>22</v>
       </c>
     </row>
     <row r="84" spans="1:7" x14ac:dyDescent="0.35">
@@ -2723,13 +2916,22 @@
         <v>15</v>
       </c>
       <c r="B84" t="s">
-        <v>56</v>
+        <v>46</v>
       </c>
       <c r="C84" s="1">
         <v>46097</v>
       </c>
+      <c r="D84" t="s">
+        <v>106</v>
+      </c>
+      <c r="E84" t="s">
+        <v>105</v>
+      </c>
+      <c r="F84" t="s">
+        <v>23</v>
+      </c>
       <c r="G84" t="s">
-        <v>31</v>
+        <v>24</v>
       </c>
     </row>
     <row r="85" spans="1:7" x14ac:dyDescent="0.35">
@@ -2737,13 +2939,19 @@
         <v>15</v>
       </c>
       <c r="B85" t="s">
-        <v>56</v>
+        <v>46</v>
       </c>
       <c r="C85" s="1">
         <v>46098</v>
       </c>
+      <c r="D85" t="s">
+        <v>103</v>
+      </c>
+      <c r="E85" t="s">
+        <v>105</v>
+      </c>
       <c r="G85" t="s">
-        <v>31</v>
+        <v>24</v>
       </c>
     </row>
     <row r="86" spans="1:7" x14ac:dyDescent="0.35">
@@ -2751,16 +2959,22 @@
         <v>15</v>
       </c>
       <c r="B86" t="s">
-        <v>56</v>
+        <v>46</v>
       </c>
       <c r="C86" s="1">
         <v>46099</v>
       </c>
+      <c r="D86" t="s">
+        <v>103</v>
+      </c>
+      <c r="E86" t="s">
+        <v>104</v>
+      </c>
       <c r="F86" t="s">
-        <v>94</v>
+        <v>78</v>
       </c>
       <c r="G86" t="s">
-        <v>33</v>
+        <v>26</v>
       </c>
     </row>
     <row r="87" spans="1:7" x14ac:dyDescent="0.35">
@@ -2768,13 +2982,16 @@
         <v>15</v>
       </c>
       <c r="B87" t="s">
-        <v>56</v>
+        <v>46</v>
       </c>
       <c r="C87" s="1">
         <v>46100</v>
       </c>
+      <c r="D87" t="s">
+        <v>103</v>
+      </c>
       <c r="G87" t="s">
-        <v>31</v>
+        <v>24</v>
       </c>
     </row>
     <row r="88" spans="1:7" x14ac:dyDescent="0.35">
@@ -2782,13 +2999,19 @@
         <v>15</v>
       </c>
       <c r="B88" t="s">
-        <v>56</v>
+        <v>46</v>
       </c>
       <c r="C88" s="1">
         <v>46101</v>
       </c>
+      <c r="D88" t="s">
+        <v>103</v>
+      </c>
+      <c r="E88" t="s">
+        <v>103</v>
+      </c>
       <c r="G88" t="s">
-        <v>31</v>
+        <v>24</v>
       </c>
     </row>
     <row r="89" spans="1:7" x14ac:dyDescent="0.35">
@@ -2796,13 +3019,19 @@
         <v>15</v>
       </c>
       <c r="B89" t="s">
-        <v>56</v>
+        <v>46</v>
       </c>
       <c r="C89" s="1">
         <v>46104</v>
       </c>
+      <c r="D89" t="s">
+        <v>103</v>
+      </c>
+      <c r="E89" t="s">
+        <v>103</v>
+      </c>
       <c r="G89" t="s">
-        <v>25</v>
+        <v>20</v>
       </c>
     </row>
     <row r="90" spans="1:7" x14ac:dyDescent="0.35">
@@ -2810,13 +3039,19 @@
         <v>15</v>
       </c>
       <c r="B90" t="s">
-        <v>56</v>
+        <v>46</v>
       </c>
       <c r="C90" s="1">
         <v>46105</v>
       </c>
+      <c r="D90" t="s">
+        <v>103</v>
+      </c>
+      <c r="E90" t="s">
+        <v>103</v>
+      </c>
       <c r="G90" t="s">
-        <v>37</v>
+        <v>29</v>
       </c>
     </row>
     <row r="91" spans="1:7" x14ac:dyDescent="0.35">
@@ -2824,13 +3059,19 @@
         <v>15</v>
       </c>
       <c r="B91" t="s">
-        <v>56</v>
+        <v>46</v>
       </c>
       <c r="C91" s="1">
         <v>46106</v>
       </c>
+      <c r="D91" t="s">
+        <v>103</v>
+      </c>
+      <c r="E91" t="s">
+        <v>103</v>
+      </c>
       <c r="G91" t="s">
-        <v>23</v>
+        <v>19</v>
       </c>
     </row>
     <row r="92" spans="1:7" x14ac:dyDescent="0.35">
@@ -2838,13 +3079,19 @@
         <v>15</v>
       </c>
       <c r="B92" t="s">
-        <v>56</v>
+        <v>46</v>
       </c>
       <c r="C92" s="1">
         <v>46107</v>
       </c>
+      <c r="D92" t="s">
+        <v>103</v>
+      </c>
+      <c r="E92" t="s">
+        <v>103</v>
+      </c>
       <c r="G92" t="s">
-        <v>23</v>
+        <v>19</v>
       </c>
     </row>
     <row r="93" spans="1:7" x14ac:dyDescent="0.35">
@@ -2852,19 +3099,19 @@
         <v>15</v>
       </c>
       <c r="B93" t="s">
-        <v>56</v>
+        <v>46</v>
       </c>
       <c r="C93" s="1">
         <v>46108</v>
       </c>
       <c r="D93" t="s">
-        <v>67</v>
+        <v>103</v>
       </c>
       <c r="E93" t="s">
-        <v>67</v>
+        <v>103</v>
       </c>
       <c r="G93" t="s">
-        <v>39</v>
+        <v>31</v>
       </c>
     </row>
     <row r="94" spans="1:7" x14ac:dyDescent="0.35">
@@ -2872,22 +3119,22 @@
         <v>15</v>
       </c>
       <c r="B94" t="s">
-        <v>56</v>
+        <v>46</v>
       </c>
       <c r="C94" s="1">
         <v>46111</v>
       </c>
       <c r="D94" t="s">
-        <v>87</v>
+        <v>72</v>
       </c>
       <c r="E94" t="s">
-        <v>87</v>
+        <v>72</v>
       </c>
       <c r="F94" t="s">
-        <v>40</v>
+        <v>32</v>
       </c>
       <c r="G94" t="s">
-        <v>41</v>
+        <v>33</v>
       </c>
     </row>
     <row r="95" spans="1:7" x14ac:dyDescent="0.35">
@@ -2895,22 +3142,22 @@
         <v>15</v>
       </c>
       <c r="B95" t="s">
-        <v>56</v>
+        <v>46</v>
       </c>
       <c r="C95" s="1">
         <v>46112</v>
       </c>
       <c r="D95" t="s">
-        <v>87</v>
+        <v>72</v>
       </c>
       <c r="E95" t="s">
-        <v>87</v>
+        <v>72</v>
       </c>
       <c r="F95" t="s">
-        <v>40</v>
+        <v>32</v>
       </c>
       <c r="G95" t="s">
-        <v>41</v>
+        <v>33</v>
       </c>
     </row>
     <row r="96" spans="1:7" x14ac:dyDescent="0.35">
@@ -2918,22 +3165,22 @@
         <v>15</v>
       </c>
       <c r="B96" t="s">
-        <v>56</v>
+        <v>46</v>
       </c>
       <c r="C96" s="1">
         <v>46113</v>
       </c>
       <c r="D96" t="s">
-        <v>87</v>
+        <v>72</v>
       </c>
       <c r="E96" t="s">
-        <v>87</v>
+        <v>72</v>
       </c>
       <c r="F96" t="s">
-        <v>40</v>
+        <v>32</v>
       </c>
       <c r="G96" t="s">
-        <v>41</v>
+        <v>33</v>
       </c>
     </row>
     <row r="97" spans="1:7" x14ac:dyDescent="0.35">
@@ -2941,22 +3188,22 @@
         <v>15</v>
       </c>
       <c r="B97" t="s">
-        <v>56</v>
+        <v>46</v>
       </c>
       <c r="C97" s="1">
         <v>46114</v>
       </c>
       <c r="D97" t="s">
-        <v>87</v>
+        <v>72</v>
       </c>
       <c r="E97" t="s">
-        <v>87</v>
+        <v>72</v>
       </c>
       <c r="F97" t="s">
-        <v>40</v>
+        <v>32</v>
       </c>
       <c r="G97" t="s">
-        <v>41</v>
+        <v>33</v>
       </c>
     </row>
     <row r="98" spans="1:7" x14ac:dyDescent="0.35">
@@ -2964,22 +3211,22 @@
         <v>15</v>
       </c>
       <c r="B98" t="s">
-        <v>56</v>
+        <v>46</v>
       </c>
       <c r="C98" s="1">
         <v>46115</v>
       </c>
       <c r="D98" t="s">
-        <v>87</v>
+        <v>72</v>
       </c>
       <c r="E98" t="s">
-        <v>87</v>
+        <v>72</v>
       </c>
       <c r="F98" t="s">
-        <v>40</v>
+        <v>32</v>
       </c>
       <c r="G98" t="s">
-        <v>41</v>
+        <v>33</v>
       </c>
     </row>
     <row r="99" spans="1:7" x14ac:dyDescent="0.35">
@@ -2987,13 +3234,19 @@
         <v>15</v>
       </c>
       <c r="B99" t="s">
-        <v>56</v>
+        <v>46</v>
       </c>
       <c r="C99" s="1">
         <v>46118</v>
       </c>
+      <c r="D99" t="s">
+        <v>107</v>
+      </c>
+      <c r="E99" t="s">
+        <v>103</v>
+      </c>
       <c r="G99" t="s">
-        <v>44</v>
+        <v>35</v>
       </c>
     </row>
     <row r="100" spans="1:7" x14ac:dyDescent="0.35">
@@ -3001,13 +3254,16 @@
         <v>15</v>
       </c>
       <c r="B100" t="s">
-        <v>56</v>
+        <v>46</v>
       </c>
       <c r="C100" s="1">
         <v>46119</v>
       </c>
+      <c r="E100" t="s">
+        <v>103</v>
+      </c>
       <c r="G100" t="s">
-        <v>23</v>
+        <v>19</v>
       </c>
     </row>
     <row r="101" spans="1:7" x14ac:dyDescent="0.35">
@@ -3015,13 +3271,16 @@
         <v>15</v>
       </c>
       <c r="B101" t="s">
-        <v>56</v>
+        <v>46</v>
       </c>
       <c r="C101" s="1">
         <v>46120</v>
       </c>
+      <c r="E101" t="s">
+        <v>103</v>
+      </c>
       <c r="G101" t="s">
-        <v>45</v>
+        <v>36</v>
       </c>
     </row>
     <row r="102" spans="1:7" x14ac:dyDescent="0.35">
@@ -3029,13 +3288,16 @@
         <v>15</v>
       </c>
       <c r="B102" t="s">
-        <v>56</v>
+        <v>46</v>
       </c>
       <c r="C102" s="1">
         <v>46121</v>
       </c>
+      <c r="E102" t="s">
+        <v>107</v>
+      </c>
       <c r="G102" t="s">
-        <v>23</v>
+        <v>19</v>
       </c>
     </row>
     <row r="103" spans="1:7" x14ac:dyDescent="0.35">
@@ -3043,13 +3305,13 @@
         <v>15</v>
       </c>
       <c r="B103" t="s">
-        <v>56</v>
+        <v>46</v>
       </c>
       <c r="C103" s="1">
         <v>46122</v>
       </c>
       <c r="G103" t="s">
-        <v>23</v>
+        <v>19</v>
       </c>
     </row>
     <row r="104" spans="1:7" x14ac:dyDescent="0.35">
@@ -3057,13 +3319,13 @@
         <v>15</v>
       </c>
       <c r="B104" t="s">
-        <v>56</v>
+        <v>46</v>
       </c>
       <c r="C104" s="1">
         <v>46125</v>
       </c>
       <c r="G104" t="s">
-        <v>23</v>
+        <v>19</v>
       </c>
     </row>
     <row r="105" spans="1:7" x14ac:dyDescent="0.35">
@@ -3071,13 +3333,13 @@
         <v>15</v>
       </c>
       <c r="B105" t="s">
-        <v>56</v>
+        <v>46</v>
       </c>
       <c r="C105" s="1">
         <v>46126</v>
       </c>
       <c r="G105" t="s">
-        <v>23</v>
+        <v>19</v>
       </c>
     </row>
     <row r="106" spans="1:7" x14ac:dyDescent="0.35">
@@ -3085,13 +3347,13 @@
         <v>15</v>
       </c>
       <c r="B106" t="s">
-        <v>56</v>
+        <v>46</v>
       </c>
       <c r="C106" s="1">
         <v>46127</v>
       </c>
       <c r="G106" t="s">
-        <v>23</v>
+        <v>19</v>
       </c>
     </row>
     <row r="107" spans="1:7" x14ac:dyDescent="0.35">
@@ -3099,22 +3361,22 @@
         <v>15</v>
       </c>
       <c r="B107" t="s">
-        <v>56</v>
+        <v>46</v>
       </c>
       <c r="C107" s="1">
         <v>46128</v>
       </c>
       <c r="D107" t="s">
-        <v>89</v>
+        <v>74</v>
       </c>
       <c r="E107" t="s">
-        <v>89</v>
+        <v>74</v>
       </c>
       <c r="F107" t="s">
-        <v>47</v>
+        <v>37</v>
       </c>
       <c r="G107" t="s">
-        <v>23</v>
+        <v>19</v>
       </c>
     </row>
     <row r="108" spans="1:7" x14ac:dyDescent="0.35">
@@ -3122,22 +3384,22 @@
         <v>15</v>
       </c>
       <c r="B108" t="s">
-        <v>56</v>
+        <v>46</v>
       </c>
       <c r="C108" s="1">
         <v>46129</v>
       </c>
       <c r="D108" t="s">
-        <v>95</v>
+        <v>79</v>
       </c>
       <c r="E108" t="s">
-        <v>95</v>
+        <v>79</v>
       </c>
       <c r="F108" t="s">
-        <v>48</v>
+        <v>38</v>
       </c>
       <c r="G108" t="s">
-        <v>49</v>
+        <v>39</v>
       </c>
     </row>
     <row r="109" spans="1:7" x14ac:dyDescent="0.35">
@@ -3145,16 +3407,16 @@
         <v>15</v>
       </c>
       <c r="B109" t="s">
-        <v>56</v>
+        <v>46</v>
       </c>
       <c r="C109" s="1">
         <v>46132</v>
       </c>
       <c r="E109" t="s">
-        <v>93</v>
+        <v>77</v>
       </c>
       <c r="G109" t="s">
-        <v>23</v>
+        <v>19</v>
       </c>
     </row>
     <row r="110" spans="1:7" x14ac:dyDescent="0.35">
@@ -3162,16 +3424,16 @@
         <v>15</v>
       </c>
       <c r="B110" t="s">
-        <v>56</v>
+        <v>46</v>
       </c>
       <c r="C110" s="1">
         <v>46133</v>
       </c>
       <c r="E110" t="s">
-        <v>77</v>
+        <v>62</v>
       </c>
       <c r="G110" t="s">
-        <v>23</v>
+        <v>19</v>
       </c>
     </row>
     <row r="111" spans="1:7" x14ac:dyDescent="0.35">
@@ -3179,16 +3441,16 @@
         <v>15</v>
       </c>
       <c r="B111" t="s">
-        <v>56</v>
+        <v>46</v>
       </c>
       <c r="C111" s="1">
         <v>46134</v>
       </c>
       <c r="D111" t="s">
-        <v>42</v>
+        <v>34</v>
       </c>
       <c r="G111" t="s">
-        <v>23</v>
+        <v>19</v>
       </c>
     </row>
     <row r="112" spans="1:7" x14ac:dyDescent="0.35">
@@ -3196,16 +3458,16 @@
         <v>15</v>
       </c>
       <c r="B112" t="s">
-        <v>56</v>
+        <v>46</v>
       </c>
       <c r="C112" s="1">
         <v>46135</v>
       </c>
       <c r="D112" t="s">
-        <v>42</v>
+        <v>34</v>
       </c>
       <c r="G112" t="s">
-        <v>23</v>
+        <v>19</v>
       </c>
     </row>
     <row r="113" spans="1:7" x14ac:dyDescent="0.35">
@@ -3213,16 +3475,16 @@
         <v>15</v>
       </c>
       <c r="B113" t="s">
-        <v>56</v>
+        <v>46</v>
       </c>
       <c r="C113" s="1">
         <v>46136</v>
       </c>
       <c r="D113" t="s">
-        <v>42</v>
+        <v>34</v>
       </c>
       <c r="G113" t="s">
-        <v>23</v>
+        <v>19</v>
       </c>
     </row>
     <row r="114" spans="1:7" x14ac:dyDescent="0.35">
@@ -3230,16 +3492,16 @@
         <v>15</v>
       </c>
       <c r="B114" t="s">
-        <v>56</v>
+        <v>46</v>
       </c>
       <c r="C114" s="1">
         <v>46139</v>
       </c>
       <c r="D114" t="s">
-        <v>42</v>
+        <v>34</v>
       </c>
       <c r="G114" t="s">
-        <v>23</v>
+        <v>19</v>
       </c>
     </row>
     <row r="115" spans="1:7" x14ac:dyDescent="0.35">
@@ -3247,16 +3509,16 @@
         <v>15</v>
       </c>
       <c r="B115" t="s">
-        <v>56</v>
+        <v>46</v>
       </c>
       <c r="C115" s="1">
         <v>46140</v>
       </c>
       <c r="D115" t="s">
-        <v>42</v>
+        <v>34</v>
       </c>
       <c r="G115" t="s">
-        <v>23</v>
+        <v>19</v>
       </c>
     </row>
     <row r="116" spans="1:7" x14ac:dyDescent="0.35">
@@ -3264,16 +3526,16 @@
         <v>15</v>
       </c>
       <c r="B116" t="s">
-        <v>56</v>
+        <v>46</v>
       </c>
       <c r="C116" s="1">
         <v>46141</v>
       </c>
       <c r="E116" t="s">
-        <v>42</v>
+        <v>34</v>
       </c>
       <c r="G116" t="s">
-        <v>23</v>
+        <v>19</v>
       </c>
     </row>
     <row r="117" spans="1:7" x14ac:dyDescent="0.35">
@@ -3281,16 +3543,16 @@
         <v>15</v>
       </c>
       <c r="B117" t="s">
-        <v>56</v>
+        <v>46</v>
       </c>
       <c r="C117" s="1">
         <v>46142</v>
       </c>
       <c r="E117" t="s">
-        <v>42</v>
+        <v>34</v>
       </c>
       <c r="G117" t="s">
-        <v>23</v>
+        <v>19</v>
       </c>
     </row>
     <row r="118" spans="1:7" x14ac:dyDescent="0.35">
@@ -3298,16 +3560,16 @@
         <v>15</v>
       </c>
       <c r="B118" t="s">
-        <v>56</v>
+        <v>46</v>
       </c>
       <c r="C118" s="1">
         <v>46143</v>
       </c>
       <c r="E118" t="s">
-        <v>42</v>
+        <v>34</v>
       </c>
       <c r="G118" t="s">
-        <v>73</v>
+        <v>58</v>
       </c>
     </row>
     <row r="119" spans="1:7" x14ac:dyDescent="0.35">
@@ -3315,16 +3577,16 @@
         <v>15</v>
       </c>
       <c r="B119" t="s">
-        <v>56</v>
+        <v>46</v>
       </c>
       <c r="C119" s="1">
         <v>46146</v>
       </c>
       <c r="E119" t="s">
-        <v>42</v>
+        <v>34</v>
       </c>
       <c r="G119" t="s">
-        <v>23</v>
+        <v>19</v>
       </c>
     </row>
     <row r="120" spans="1:7" x14ac:dyDescent="0.35">
@@ -3332,16 +3594,16 @@
         <v>15</v>
       </c>
       <c r="B120" t="s">
-        <v>56</v>
+        <v>46</v>
       </c>
       <c r="C120" s="1">
         <v>46147</v>
       </c>
       <c r="E120" t="s">
+        <v>34</v>
+      </c>
+      <c r="G120" t="s">
         <v>42</v>
-      </c>
-      <c r="G120" t="s">
-        <v>52</v>
       </c>
     </row>
     <row r="121" spans="1:7" x14ac:dyDescent="0.35">
@@ -3349,13 +3611,13 @@
         <v>15</v>
       </c>
       <c r="B121" t="s">
-        <v>56</v>
+        <v>46</v>
       </c>
       <c r="C121" s="1">
         <v>46148</v>
       </c>
       <c r="G121" t="s">
-        <v>23</v>
+        <v>19</v>
       </c>
     </row>
     <row r="122" spans="1:7" x14ac:dyDescent="0.35">
@@ -3363,13 +3625,13 @@
         <v>15</v>
       </c>
       <c r="B122" t="s">
-        <v>56</v>
+        <v>46</v>
       </c>
       <c r="C122" s="1">
         <v>46149</v>
       </c>
       <c r="G122" t="s">
-        <v>23</v>
+        <v>19</v>
       </c>
     </row>
     <row r="123" spans="1:7" x14ac:dyDescent="0.35">
@@ -3377,13 +3639,13 @@
         <v>15</v>
       </c>
       <c r="B123" t="s">
-        <v>56</v>
+        <v>46</v>
       </c>
       <c r="C123" s="1">
         <v>46150</v>
       </c>
       <c r="G123" t="s">
-        <v>74</v>
+        <v>59</v>
       </c>
     </row>
     <row r="124" spans="1:7" x14ac:dyDescent="0.35">
@@ -3391,13 +3653,13 @@
         <v>15</v>
       </c>
       <c r="B124" t="s">
-        <v>56</v>
+        <v>46</v>
       </c>
       <c r="C124" s="1">
         <v>46153</v>
       </c>
       <c r="G124" t="s">
-        <v>23</v>
+        <v>19</v>
       </c>
     </row>
     <row r="125" spans="1:7" x14ac:dyDescent="0.35">
@@ -3405,13 +3667,13 @@
         <v>15</v>
       </c>
       <c r="B125" t="s">
-        <v>56</v>
+        <v>46</v>
       </c>
       <c r="C125" s="1">
         <v>46154</v>
       </c>
       <c r="G125" t="s">
-        <v>23</v>
+        <v>19</v>
       </c>
     </row>
     <row r="126" spans="1:7" x14ac:dyDescent="0.35">
@@ -3419,13 +3681,13 @@
         <v>15</v>
       </c>
       <c r="B126" t="s">
-        <v>56</v>
+        <v>46</v>
       </c>
       <c r="C126" s="1">
         <v>46155</v>
       </c>
       <c r="G126" t="s">
-        <v>23</v>
+        <v>19</v>
       </c>
     </row>
     <row r="127" spans="1:7" x14ac:dyDescent="0.35">
@@ -3433,13 +3695,13 @@
         <v>15</v>
       </c>
       <c r="B127" t="s">
-        <v>56</v>
+        <v>46</v>
       </c>
       <c r="C127" s="1">
         <v>46156</v>
       </c>
       <c r="G127" t="s">
-        <v>23</v>
+        <v>19</v>
       </c>
     </row>
     <row r="128" spans="1:7" x14ac:dyDescent="0.35">
@@ -3447,13 +3709,13 @@
         <v>15</v>
       </c>
       <c r="B128" t="s">
-        <v>56</v>
+        <v>46</v>
       </c>
       <c r="C128" s="1">
         <v>46157</v>
       </c>
       <c r="G128" t="s">
-        <v>23</v>
+        <v>19</v>
       </c>
     </row>
     <row r="129" spans="1:7" x14ac:dyDescent="0.35">
@@ -3461,13 +3723,13 @@
         <v>15</v>
       </c>
       <c r="B129" t="s">
-        <v>56</v>
+        <v>46</v>
       </c>
       <c r="C129" s="1">
         <v>46160</v>
       </c>
       <c r="G129" t="s">
-        <v>23</v>
+        <v>19</v>
       </c>
     </row>
     <row r="130" spans="1:7" x14ac:dyDescent="0.35">
@@ -3475,13 +3737,13 @@
         <v>15</v>
       </c>
       <c r="B130" t="s">
-        <v>56</v>
+        <v>46</v>
       </c>
       <c r="C130" s="1">
         <v>46161</v>
       </c>
       <c r="G130" t="s">
-        <v>23</v>
+        <v>19</v>
       </c>
     </row>
     <row r="131" spans="1:7" x14ac:dyDescent="0.35">
@@ -3489,13 +3751,13 @@
         <v>15</v>
       </c>
       <c r="B131" t="s">
-        <v>56</v>
+        <v>46</v>
       </c>
       <c r="C131" s="1">
         <v>46162</v>
       </c>
       <c r="G131" t="s">
-        <v>23</v>
+        <v>19</v>
       </c>
     </row>
     <row r="132" spans="1:7" x14ac:dyDescent="0.35">
@@ -3503,13 +3765,13 @@
         <v>15</v>
       </c>
       <c r="B132" t="s">
-        <v>56</v>
+        <v>46</v>
       </c>
       <c r="C132" s="1">
         <v>46163</v>
       </c>
       <c r="G132" t="s">
-        <v>23</v>
+        <v>19</v>
       </c>
     </row>
     <row r="133" spans="1:7" x14ac:dyDescent="0.35">
@@ -3517,22 +3779,22 @@
         <v>15</v>
       </c>
       <c r="B133" t="s">
-        <v>56</v>
+        <v>46</v>
       </c>
       <c r="C133" s="1">
         <v>46164</v>
       </c>
       <c r="D133" t="s">
-        <v>89</v>
+        <v>74</v>
       </c>
       <c r="E133" t="s">
-        <v>89</v>
+        <v>74</v>
       </c>
       <c r="F133" t="s">
-        <v>53</v>
+        <v>43</v>
       </c>
       <c r="G133" t="s">
-        <v>23</v>
+        <v>19</v>
       </c>
     </row>
     <row r="134" spans="1:7" x14ac:dyDescent="0.35">
@@ -3540,22 +3802,22 @@
         <v>15</v>
       </c>
       <c r="B134" t="s">
-        <v>56</v>
+        <v>46</v>
       </c>
       <c r="C134" s="1">
         <v>46167</v>
       </c>
       <c r="D134" t="s">
-        <v>89</v>
+        <v>74</v>
       </c>
       <c r="E134" t="s">
-        <v>89</v>
+        <v>74</v>
       </c>
       <c r="F134" t="s">
-        <v>54</v>
+        <v>44</v>
       </c>
       <c r="G134" t="s">
-        <v>55</v>
+        <v>45</v>
       </c>
     </row>
     <row r="135" spans="1:7" x14ac:dyDescent="0.35">
@@ -3563,13 +3825,13 @@
         <v>15</v>
       </c>
       <c r="B135" t="s">
-        <v>56</v>
+        <v>46</v>
       </c>
       <c r="C135" s="1">
         <v>46168</v>
       </c>
       <c r="G135" t="s">
-        <v>23</v>
+        <v>19</v>
       </c>
     </row>
     <row r="136" spans="1:7" x14ac:dyDescent="0.35">
@@ -3577,13 +3839,13 @@
         <v>15</v>
       </c>
       <c r="B136" t="s">
-        <v>56</v>
+        <v>46</v>
       </c>
       <c r="C136" s="1">
         <v>46169</v>
       </c>
       <c r="G136" t="s">
-        <v>23</v>
+        <v>19</v>
       </c>
     </row>
     <row r="137" spans="1:7" x14ac:dyDescent="0.35">
@@ -3591,13 +3853,13 @@
         <v>15</v>
       </c>
       <c r="B137" t="s">
-        <v>56</v>
+        <v>46</v>
       </c>
       <c r="C137" s="1">
         <v>46170</v>
       </c>
       <c r="G137" t="s">
-        <v>23</v>
+        <v>19</v>
       </c>
     </row>
     <row r="138" spans="1:7" x14ac:dyDescent="0.35">
@@ -3605,13 +3867,13 @@
         <v>15</v>
       </c>
       <c r="B138" t="s">
-        <v>56</v>
+        <v>46</v>
       </c>
       <c r="C138" s="1">
         <v>46171</v>
       </c>
       <c r="G138" t="s">
-        <v>74</v>
+        <v>59</v>
       </c>
     </row>
     <row r="139" spans="1:7" x14ac:dyDescent="0.35">
@@ -3619,13 +3881,13 @@
         <v>15</v>
       </c>
       <c r="B139" t="s">
-        <v>56</v>
+        <v>46</v>
       </c>
       <c r="C139" s="1">
         <v>46174</v>
       </c>
       <c r="G139" t="s">
-        <v>23</v>
+        <v>19</v>
       </c>
     </row>
     <row r="140" spans="1:7" x14ac:dyDescent="0.35">
@@ -3633,13 +3895,13 @@
         <v>15</v>
       </c>
       <c r="B140" t="s">
-        <v>56</v>
+        <v>46</v>
       </c>
       <c r="C140" s="1">
         <v>46175</v>
       </c>
       <c r="G140" t="s">
-        <v>23</v>
+        <v>19</v>
       </c>
     </row>
     <row r="141" spans="1:7" x14ac:dyDescent="0.35">
@@ -3647,13 +3909,13 @@
         <v>15</v>
       </c>
       <c r="B141" t="s">
-        <v>56</v>
+        <v>46</v>
       </c>
       <c r="C141" s="1">
         <v>46176</v>
       </c>
       <c r="G141" t="s">
-        <v>23</v>
+        <v>19</v>
       </c>
     </row>
     <row r="142" spans="1:7" x14ac:dyDescent="0.35">
@@ -3661,13 +3923,13 @@
         <v>15</v>
       </c>
       <c r="B142" t="s">
-        <v>56</v>
+        <v>46</v>
       </c>
       <c r="C142" s="1">
         <v>46177</v>
       </c>
       <c r="G142" t="s">
-        <v>23</v>
+        <v>19</v>
       </c>
     </row>
     <row r="143" spans="1:7" x14ac:dyDescent="0.35">
@@ -3675,13 +3937,13 @@
         <v>15</v>
       </c>
       <c r="B143" t="s">
-        <v>56</v>
+        <v>46</v>
       </c>
       <c r="C143" s="1">
         <v>46178</v>
       </c>
       <c r="G143" t="s">
-        <v>75</v>
+        <v>60</v>
       </c>
     </row>
     <row r="144" spans="1:7" x14ac:dyDescent="0.35">
@@ -3689,13 +3951,13 @@
         <v>15</v>
       </c>
       <c r="B144" t="s">
-        <v>56</v>
+        <v>46</v>
       </c>
       <c r="C144" s="1">
         <v>46181</v>
       </c>
       <c r="G144" t="s">
-        <v>23</v>
+        <v>19</v>
       </c>
     </row>
     <row r="145" spans="1:7" x14ac:dyDescent="0.35">
@@ -3703,13 +3965,13 @@
         <v>15</v>
       </c>
       <c r="B145" t="s">
-        <v>56</v>
+        <v>46</v>
       </c>
       <c r="C145" s="1">
         <v>46182</v>
       </c>
       <c r="G145" t="s">
-        <v>23</v>
+        <v>19</v>
       </c>
     </row>
     <row r="146" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
@@ -3717,13 +3979,13 @@
         <v>15</v>
       </c>
       <c r="B146" t="s">
-        <v>76</v>
+        <v>61</v>
       </c>
       <c r="C146" s="1">
         <v>46086</v>
       </c>
       <c r="G146" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
     </row>
     <row r="147" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
@@ -3731,13 +3993,13 @@
         <v>15</v>
       </c>
       <c r="B147" t="s">
-        <v>76</v>
+        <v>61</v>
       </c>
       <c r="C147" s="1">
         <v>46087</v>
       </c>
       <c r="G147" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
     </row>
     <row r="148" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
@@ -3745,13 +4007,13 @@
         <v>15</v>
       </c>
       <c r="B148" t="s">
-        <v>76</v>
+        <v>61</v>
       </c>
       <c r="C148" s="1">
         <v>46090</v>
       </c>
       <c r="G148" t="s">
-        <v>23</v>
+        <v>19</v>
       </c>
     </row>
     <row r="149" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
@@ -3759,22 +4021,22 @@
         <v>15</v>
       </c>
       <c r="B149" t="s">
-        <v>76</v>
+        <v>61</v>
       </c>
       <c r="C149" s="1">
         <v>46091</v>
       </c>
       <c r="D149" t="s">
-        <v>77</v>
+        <v>62</v>
       </c>
       <c r="E149" t="s">
-        <v>77</v>
+        <v>62</v>
       </c>
       <c r="F149" t="s">
-        <v>78</v>
+        <v>63</v>
       </c>
       <c r="G149" t="s">
-        <v>25</v>
+        <v>20</v>
       </c>
     </row>
     <row r="150" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
@@ -3782,13 +4044,13 @@
         <v>15</v>
       </c>
       <c r="B150" t="s">
-        <v>76</v>
+        <v>61</v>
       </c>
       <c r="C150" s="1">
         <v>46092</v>
       </c>
       <c r="G150" t="s">
-        <v>23</v>
+        <v>19</v>
       </c>
     </row>
     <row r="151" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
@@ -3796,13 +4058,13 @@
         <v>15</v>
       </c>
       <c r="B151" t="s">
-        <v>76</v>
+        <v>61</v>
       </c>
       <c r="C151" s="1">
         <v>46093</v>
       </c>
       <c r="G151" t="s">
-        <v>23</v>
+        <v>19</v>
       </c>
     </row>
     <row r="152" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
@@ -3810,13 +4072,13 @@
         <v>15</v>
       </c>
       <c r="B152" t="s">
-        <v>76</v>
+        <v>61</v>
       </c>
       <c r="C152" s="1">
         <v>46094</v>
       </c>
       <c r="G152" t="s">
-        <v>29</v>
+        <v>22</v>
       </c>
     </row>
     <row r="153" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
@@ -3824,13 +4086,13 @@
         <v>15</v>
       </c>
       <c r="B153" t="s">
-        <v>76</v>
+        <v>61</v>
       </c>
       <c r="C153" s="1">
         <v>46097</v>
       </c>
       <c r="G153" t="s">
-        <v>31</v>
+        <v>24</v>
       </c>
     </row>
     <row r="154" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
@@ -3838,13 +4100,13 @@
         <v>15</v>
       </c>
       <c r="B154" t="s">
-        <v>76</v>
+        <v>61</v>
       </c>
       <c r="C154" s="1">
         <v>46098</v>
       </c>
       <c r="G154" t="s">
-        <v>31</v>
+        <v>24</v>
       </c>
     </row>
     <row r="155" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
@@ -3852,13 +4114,13 @@
         <v>15</v>
       </c>
       <c r="B155" t="s">
-        <v>76</v>
+        <v>61</v>
       </c>
       <c r="C155" s="1">
         <v>46099</v>
       </c>
       <c r="G155" t="s">
-        <v>33</v>
+        <v>26</v>
       </c>
     </row>
     <row r="156" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
@@ -3866,13 +4128,13 @@
         <v>15</v>
       </c>
       <c r="B156" t="s">
-        <v>76</v>
+        <v>61</v>
       </c>
       <c r="C156" s="1">
         <v>46100</v>
       </c>
       <c r="G156" t="s">
-        <v>31</v>
+        <v>24</v>
       </c>
     </row>
     <row r="157" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
@@ -3880,13 +4142,13 @@
         <v>15</v>
       </c>
       <c r="B157" t="s">
-        <v>76</v>
+        <v>61</v>
       </c>
       <c r="C157" s="1">
         <v>46101</v>
       </c>
       <c r="G157" t="s">
-        <v>31</v>
+        <v>24</v>
       </c>
     </row>
     <row r="158" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
@@ -3894,13 +4156,13 @@
         <v>15</v>
       </c>
       <c r="B158" t="s">
-        <v>76</v>
+        <v>61</v>
       </c>
       <c r="C158" s="1">
         <v>46104</v>
       </c>
       <c r="G158" t="s">
-        <v>25</v>
+        <v>20</v>
       </c>
     </row>
     <row r="159" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
@@ -3908,13 +4170,13 @@
         <v>15</v>
       </c>
       <c r="B159" t="s">
-        <v>76</v>
+        <v>61</v>
       </c>
       <c r="C159" s="1">
         <v>46105</v>
       </c>
       <c r="G159" t="s">
-        <v>37</v>
+        <v>29</v>
       </c>
     </row>
     <row r="160" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
@@ -3922,13 +4184,13 @@
         <v>15</v>
       </c>
       <c r="B160" t="s">
-        <v>76</v>
+        <v>61</v>
       </c>
       <c r="C160" s="1">
         <v>46106</v>
       </c>
       <c r="G160" t="s">
-        <v>23</v>
+        <v>19</v>
       </c>
     </row>
     <row r="161" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
@@ -3936,13 +4198,13 @@
         <v>15</v>
       </c>
       <c r="B161" t="s">
-        <v>76</v>
+        <v>61</v>
       </c>
       <c r="C161" s="1">
         <v>46107</v>
       </c>
       <c r="G161" t="s">
-        <v>23</v>
+        <v>19</v>
       </c>
     </row>
     <row r="162" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
@@ -3950,13 +4212,13 @@
         <v>15</v>
       </c>
       <c r="B162" t="s">
-        <v>76</v>
+        <v>61</v>
       </c>
       <c r="C162" s="1">
         <v>46108</v>
       </c>
       <c r="G162" t="s">
-        <v>39</v>
+        <v>31</v>
       </c>
     </row>
     <row r="163" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
@@ -3964,16 +4226,16 @@
         <v>15</v>
       </c>
       <c r="B163" t="s">
-        <v>76</v>
+        <v>61</v>
       </c>
       <c r="C163" s="1">
         <v>46111</v>
       </c>
       <c r="F163" t="s">
-        <v>40</v>
+        <v>32</v>
       </c>
       <c r="G163" t="s">
-        <v>41</v>
+        <v>33</v>
       </c>
     </row>
     <row r="164" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
@@ -3981,16 +4243,16 @@
         <v>15</v>
       </c>
       <c r="B164" t="s">
-        <v>76</v>
+        <v>61</v>
       </c>
       <c r="C164" s="1">
         <v>46112</v>
       </c>
       <c r="F164" t="s">
-        <v>40</v>
+        <v>32</v>
       </c>
       <c r="G164" t="s">
-        <v>41</v>
+        <v>33</v>
       </c>
     </row>
     <row r="165" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
@@ -3998,16 +4260,16 @@
         <v>15</v>
       </c>
       <c r="B165" t="s">
-        <v>76</v>
+        <v>61</v>
       </c>
       <c r="C165" s="1">
         <v>46113</v>
       </c>
       <c r="F165" t="s">
-        <v>40</v>
+        <v>32</v>
       </c>
       <c r="G165" t="s">
-        <v>41</v>
+        <v>33</v>
       </c>
     </row>
     <row r="166" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
@@ -4015,16 +4277,16 @@
         <v>15</v>
       </c>
       <c r="B166" t="s">
-        <v>76</v>
+        <v>61</v>
       </c>
       <c r="C166" s="1">
         <v>46114</v>
       </c>
       <c r="F166" t="s">
-        <v>40</v>
+        <v>32</v>
       </c>
       <c r="G166" t="s">
-        <v>41</v>
+        <v>33</v>
       </c>
     </row>
     <row r="167" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
@@ -4032,16 +4294,16 @@
         <v>15</v>
       </c>
       <c r="B167" t="s">
-        <v>76</v>
+        <v>61</v>
       </c>
       <c r="C167" s="1">
         <v>46115</v>
       </c>
       <c r="F167" t="s">
-        <v>40</v>
+        <v>32</v>
       </c>
       <c r="G167" t="s">
-        <v>41</v>
+        <v>33</v>
       </c>
     </row>
     <row r="168" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
@@ -4049,13 +4311,13 @@
         <v>15</v>
       </c>
       <c r="B168" t="s">
-        <v>76</v>
+        <v>61</v>
       </c>
       <c r="C168" s="1">
         <v>46118</v>
       </c>
       <c r="G168" t="s">
-        <v>44</v>
+        <v>35</v>
       </c>
     </row>
     <row r="169" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
@@ -4063,13 +4325,13 @@
         <v>15</v>
       </c>
       <c r="B169" t="s">
-        <v>76</v>
+        <v>61</v>
       </c>
       <c r="C169" s="1">
         <v>46119</v>
       </c>
       <c r="G169" t="s">
-        <v>23</v>
+        <v>19</v>
       </c>
     </row>
     <row r="170" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
@@ -4077,13 +4339,13 @@
         <v>15</v>
       </c>
       <c r="B170" t="s">
-        <v>76</v>
+        <v>61</v>
       </c>
       <c r="C170" s="1">
         <v>46120</v>
       </c>
       <c r="G170" t="s">
-        <v>45</v>
+        <v>36</v>
       </c>
     </row>
     <row r="171" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
@@ -4091,13 +4353,13 @@
         <v>15</v>
       </c>
       <c r="B171" t="s">
-        <v>76</v>
+        <v>61</v>
       </c>
       <c r="C171" s="1">
         <v>46121</v>
       </c>
       <c r="G171" t="s">
-        <v>23</v>
+        <v>19</v>
       </c>
     </row>
     <row r="172" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
@@ -4105,13 +4367,13 @@
         <v>15</v>
       </c>
       <c r="B172" t="s">
-        <v>76</v>
+        <v>61</v>
       </c>
       <c r="C172" s="1">
         <v>46122</v>
       </c>
       <c r="G172" t="s">
-        <v>23</v>
+        <v>19</v>
       </c>
     </row>
     <row r="173" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
@@ -4119,13 +4381,13 @@
         <v>15</v>
       </c>
       <c r="B173" t="s">
-        <v>76</v>
+        <v>61</v>
       </c>
       <c r="C173" s="1">
         <v>46125</v>
       </c>
       <c r="G173" t="s">
-        <v>23</v>
+        <v>19</v>
       </c>
     </row>
     <row r="174" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
@@ -4133,13 +4395,13 @@
         <v>15</v>
       </c>
       <c r="B174" t="s">
-        <v>76</v>
+        <v>61</v>
       </c>
       <c r="C174" s="1">
         <v>46126</v>
       </c>
       <c r="G174" t="s">
-        <v>23</v>
+        <v>19</v>
       </c>
     </row>
     <row r="175" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
@@ -4147,13 +4409,13 @@
         <v>15</v>
       </c>
       <c r="B175" t="s">
-        <v>76</v>
+        <v>61</v>
       </c>
       <c r="C175" s="1">
         <v>46127</v>
       </c>
       <c r="G175" t="s">
-        <v>23</v>
+        <v>19</v>
       </c>
     </row>
     <row r="176" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
@@ -4161,16 +4423,16 @@
         <v>15</v>
       </c>
       <c r="B176" t="s">
-        <v>76</v>
+        <v>61</v>
       </c>
       <c r="C176" s="1">
         <v>46128</v>
       </c>
       <c r="F176" t="s">
-        <v>47</v>
+        <v>37</v>
       </c>
       <c r="G176" t="s">
-        <v>23</v>
+        <v>19</v>
       </c>
     </row>
     <row r="177" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
@@ -4178,16 +4440,16 @@
         <v>15</v>
       </c>
       <c r="B177" t="s">
-        <v>76</v>
+        <v>61</v>
       </c>
       <c r="C177" s="1">
         <v>46129</v>
       </c>
       <c r="F177" t="s">
-        <v>48</v>
+        <v>38</v>
       </c>
       <c r="G177" t="s">
-        <v>49</v>
+        <v>39</v>
       </c>
     </row>
     <row r="178" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
@@ -4195,13 +4457,13 @@
         <v>15</v>
       </c>
       <c r="B178" t="s">
-        <v>76</v>
+        <v>61</v>
       </c>
       <c r="C178" s="1">
         <v>46132</v>
       </c>
       <c r="G178" t="s">
-        <v>23</v>
+        <v>19</v>
       </c>
     </row>
     <row r="179" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
@@ -4209,19 +4471,19 @@
         <v>15</v>
       </c>
       <c r="B179" t="s">
-        <v>76</v>
+        <v>61</v>
       </c>
       <c r="C179" s="1">
         <v>46133</v>
       </c>
       <c r="E179" t="s">
-        <v>77</v>
+        <v>62</v>
       </c>
       <c r="F179" t="s">
-        <v>79</v>
+        <v>64</v>
       </c>
       <c r="G179" t="s">
-        <v>23</v>
+        <v>19</v>
       </c>
     </row>
     <row r="180" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
@@ -4229,13 +4491,13 @@
         <v>15</v>
       </c>
       <c r="B180" t="s">
-        <v>76</v>
+        <v>61</v>
       </c>
       <c r="C180" s="1">
         <v>46134</v>
       </c>
       <c r="G180" t="s">
-        <v>23</v>
+        <v>19</v>
       </c>
     </row>
     <row r="181" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
@@ -4243,13 +4505,13 @@
         <v>15</v>
       </c>
       <c r="B181" t="s">
-        <v>76</v>
+        <v>61</v>
       </c>
       <c r="C181" s="1">
         <v>46135</v>
       </c>
       <c r="G181" t="s">
-        <v>23</v>
+        <v>19</v>
       </c>
     </row>
     <row r="182" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
@@ -4257,13 +4519,13 @@
         <v>15</v>
       </c>
       <c r="B182" t="s">
-        <v>76</v>
+        <v>61</v>
       </c>
       <c r="C182" s="1">
         <v>46136</v>
       </c>
       <c r="G182" t="s">
-        <v>23</v>
+        <v>19</v>
       </c>
     </row>
     <row r="183" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
@@ -4271,13 +4533,13 @@
         <v>15</v>
       </c>
       <c r="B183" t="s">
-        <v>76</v>
+        <v>61</v>
       </c>
       <c r="C183" s="1">
         <v>46139</v>
       </c>
       <c r="G183" t="s">
-        <v>23</v>
+        <v>19</v>
       </c>
     </row>
     <row r="184" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
@@ -4285,13 +4547,13 @@
         <v>15</v>
       </c>
       <c r="B184" t="s">
-        <v>76</v>
+        <v>61</v>
       </c>
       <c r="C184" s="1">
         <v>46140</v>
       </c>
       <c r="G184" t="s">
-        <v>23</v>
+        <v>19</v>
       </c>
     </row>
     <row r="185" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
@@ -4299,13 +4561,13 @@
         <v>15</v>
       </c>
       <c r="B185" t="s">
-        <v>76</v>
+        <v>61</v>
       </c>
       <c r="C185" s="1">
         <v>46141</v>
       </c>
       <c r="G185" t="s">
-        <v>23</v>
+        <v>19</v>
       </c>
     </row>
     <row r="186" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
@@ -4313,13 +4575,13 @@
         <v>15</v>
       </c>
       <c r="B186" t="s">
-        <v>76</v>
+        <v>61</v>
       </c>
       <c r="C186" s="1">
         <v>46142</v>
       </c>
       <c r="G186" t="s">
-        <v>23</v>
+        <v>19</v>
       </c>
     </row>
     <row r="187" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
@@ -4327,13 +4589,13 @@
         <v>15</v>
       </c>
       <c r="B187" t="s">
-        <v>76</v>
+        <v>61</v>
       </c>
       <c r="C187" s="1">
         <v>46143</v>
       </c>
       <c r="G187" t="s">
-        <v>73</v>
+        <v>58</v>
       </c>
     </row>
     <row r="188" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
@@ -4341,13 +4603,13 @@
         <v>15</v>
       </c>
       <c r="B188" t="s">
-        <v>76</v>
+        <v>61</v>
       </c>
       <c r="C188" s="1">
         <v>46146</v>
       </c>
       <c r="G188" t="s">
-        <v>23</v>
+        <v>19</v>
       </c>
     </row>
     <row r="189" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
@@ -4355,13 +4617,13 @@
         <v>15</v>
       </c>
       <c r="B189" t="s">
-        <v>76</v>
+        <v>61</v>
       </c>
       <c r="C189" s="1">
         <v>46147</v>
       </c>
       <c r="G189" t="s">
-        <v>52</v>
+        <v>42</v>
       </c>
     </row>
     <row r="190" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
@@ -4369,13 +4631,13 @@
         <v>15</v>
       </c>
       <c r="B190" t="s">
-        <v>76</v>
+        <v>61</v>
       </c>
       <c r="C190" s="1">
         <v>46148</v>
       </c>
       <c r="G190" t="s">
-        <v>23</v>
+        <v>19</v>
       </c>
     </row>
     <row r="191" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
@@ -4383,13 +4645,13 @@
         <v>15</v>
       </c>
       <c r="B191" t="s">
-        <v>76</v>
+        <v>61</v>
       </c>
       <c r="C191" s="1">
         <v>46149</v>
       </c>
       <c r="G191" t="s">
-        <v>23</v>
+        <v>19</v>
       </c>
     </row>
     <row r="192" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
@@ -4397,13 +4659,13 @@
         <v>15</v>
       </c>
       <c r="B192" t="s">
-        <v>76</v>
+        <v>61</v>
       </c>
       <c r="C192" s="1">
         <v>46150</v>
       </c>
       <c r="G192" t="s">
-        <v>74</v>
+        <v>59</v>
       </c>
     </row>
     <row r="193" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
@@ -4411,13 +4673,13 @@
         <v>15</v>
       </c>
       <c r="B193" t="s">
-        <v>76</v>
+        <v>61</v>
       </c>
       <c r="C193" s="1">
         <v>46153</v>
       </c>
       <c r="G193" t="s">
-        <v>23</v>
+        <v>19</v>
       </c>
     </row>
     <row r="194" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
@@ -4425,13 +4687,13 @@
         <v>15</v>
       </c>
       <c r="B194" t="s">
-        <v>76</v>
+        <v>61</v>
       </c>
       <c r="C194" s="1">
         <v>46154</v>
       </c>
       <c r="G194" t="s">
-        <v>23</v>
+        <v>19</v>
       </c>
     </row>
     <row r="195" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
@@ -4439,13 +4701,13 @@
         <v>15</v>
       </c>
       <c r="B195" t="s">
-        <v>76</v>
+        <v>61</v>
       </c>
       <c r="C195" s="1">
         <v>46155</v>
       </c>
       <c r="G195" t="s">
-        <v>23</v>
+        <v>19</v>
       </c>
     </row>
     <row r="196" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
@@ -4453,13 +4715,13 @@
         <v>15</v>
       </c>
       <c r="B196" t="s">
-        <v>76</v>
+        <v>61</v>
       </c>
       <c r="C196" s="1">
         <v>46156</v>
       </c>
       <c r="G196" t="s">
-        <v>23</v>
+        <v>19</v>
       </c>
     </row>
     <row r="197" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
@@ -4467,13 +4729,13 @@
         <v>15</v>
       </c>
       <c r="B197" t="s">
-        <v>76</v>
+        <v>61</v>
       </c>
       <c r="C197" s="1">
         <v>46157</v>
       </c>
       <c r="G197" t="s">
-        <v>23</v>
+        <v>19</v>
       </c>
     </row>
     <row r="198" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
@@ -4481,13 +4743,13 @@
         <v>15</v>
       </c>
       <c r="B198" t="s">
-        <v>76</v>
+        <v>61</v>
       </c>
       <c r="C198" s="1">
         <v>46160</v>
       </c>
       <c r="G198" t="s">
-        <v>23</v>
+        <v>19</v>
       </c>
     </row>
     <row r="199" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
@@ -4495,13 +4757,13 @@
         <v>15</v>
       </c>
       <c r="B199" t="s">
-        <v>76</v>
+        <v>61</v>
       </c>
       <c r="C199" s="1">
         <v>46161</v>
       </c>
       <c r="G199" t="s">
-        <v>23</v>
+        <v>19</v>
       </c>
     </row>
     <row r="200" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
@@ -4509,13 +4771,13 @@
         <v>15</v>
       </c>
       <c r="B200" t="s">
-        <v>76</v>
+        <v>61</v>
       </c>
       <c r="C200" s="1">
         <v>46162</v>
       </c>
       <c r="G200" t="s">
-        <v>23</v>
+        <v>19</v>
       </c>
     </row>
     <row r="201" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
@@ -4523,13 +4785,13 @@
         <v>15</v>
       </c>
       <c r="B201" t="s">
-        <v>76</v>
+        <v>61</v>
       </c>
       <c r="C201" s="1">
         <v>46163</v>
       </c>
       <c r="G201" t="s">
-        <v>23</v>
+        <v>19</v>
       </c>
     </row>
     <row r="202" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
@@ -4537,16 +4799,16 @@
         <v>15</v>
       </c>
       <c r="B202" t="s">
-        <v>76</v>
+        <v>61</v>
       </c>
       <c r="C202" s="1">
         <v>46164</v>
       </c>
       <c r="F202" t="s">
-        <v>53</v>
+        <v>43</v>
       </c>
       <c r="G202" t="s">
-        <v>23</v>
+        <v>19</v>
       </c>
     </row>
     <row r="203" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
@@ -4554,16 +4816,16 @@
         <v>15</v>
       </c>
       <c r="B203" t="s">
-        <v>76</v>
+        <v>61</v>
       </c>
       <c r="C203" s="1">
         <v>46167</v>
       </c>
       <c r="F203" t="s">
-        <v>54</v>
+        <v>44</v>
       </c>
       <c r="G203" t="s">
-        <v>55</v>
+        <v>45</v>
       </c>
     </row>
     <row r="204" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
@@ -4571,13 +4833,13 @@
         <v>15</v>
       </c>
       <c r="B204" t="s">
-        <v>76</v>
+        <v>61</v>
       </c>
       <c r="C204" s="1">
         <v>46168</v>
       </c>
       <c r="G204" t="s">
-        <v>23</v>
+        <v>19</v>
       </c>
     </row>
     <row r="205" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
@@ -4585,13 +4847,13 @@
         <v>15</v>
       </c>
       <c r="B205" t="s">
-        <v>76</v>
+        <v>61</v>
       </c>
       <c r="C205" s="1">
         <v>46169</v>
       </c>
       <c r="G205" t="s">
-        <v>23</v>
+        <v>19</v>
       </c>
     </row>
     <row r="206" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
@@ -4599,13 +4861,13 @@
         <v>15</v>
       </c>
       <c r="B206" t="s">
-        <v>76</v>
+        <v>61</v>
       </c>
       <c r="C206" s="1">
         <v>46170</v>
       </c>
       <c r="G206" t="s">
-        <v>23</v>
+        <v>19</v>
       </c>
     </row>
     <row r="207" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
@@ -4613,13 +4875,13 @@
         <v>15</v>
       </c>
       <c r="B207" t="s">
-        <v>76</v>
+        <v>61</v>
       </c>
       <c r="C207" s="1">
         <v>46171</v>
       </c>
       <c r="G207" t="s">
-        <v>74</v>
+        <v>59</v>
       </c>
     </row>
     <row r="208" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
@@ -4627,13 +4889,13 @@
         <v>15</v>
       </c>
       <c r="B208" t="s">
-        <v>76</v>
+        <v>61</v>
       </c>
       <c r="C208" s="1">
         <v>46174</v>
       </c>
       <c r="G208" t="s">
-        <v>23</v>
+        <v>19</v>
       </c>
     </row>
     <row r="209" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
@@ -4641,13 +4903,13 @@
         <v>15</v>
       </c>
       <c r="B209" t="s">
-        <v>76</v>
+        <v>61</v>
       </c>
       <c r="C209" s="1">
         <v>46175</v>
       </c>
       <c r="G209" t="s">
-        <v>23</v>
+        <v>19</v>
       </c>
     </row>
     <row r="210" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
@@ -4655,13 +4917,13 @@
         <v>15</v>
       </c>
       <c r="B210" t="s">
-        <v>76</v>
+        <v>61</v>
       </c>
       <c r="C210" s="1">
         <v>46176</v>
       </c>
       <c r="G210" t="s">
-        <v>23</v>
+        <v>19</v>
       </c>
     </row>
     <row r="211" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
@@ -4669,13 +4931,13 @@
         <v>15</v>
       </c>
       <c r="B211" t="s">
-        <v>76</v>
+        <v>61</v>
       </c>
       <c r="C211" s="1">
         <v>46177</v>
       </c>
       <c r="G211" t="s">
-        <v>23</v>
+        <v>19</v>
       </c>
     </row>
     <row r="212" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
@@ -4683,13 +4945,13 @@
         <v>15</v>
       </c>
       <c r="B212" t="s">
-        <v>76</v>
+        <v>61</v>
       </c>
       <c r="C212" s="1">
         <v>46178</v>
       </c>
       <c r="G212" t="s">
-        <v>75</v>
+        <v>60</v>
       </c>
     </row>
     <row r="213" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
@@ -4697,13 +4959,13 @@
         <v>15</v>
       </c>
       <c r="B213" t="s">
-        <v>76</v>
+        <v>61</v>
       </c>
       <c r="C213" s="1">
         <v>46181</v>
       </c>
       <c r="G213" t="s">
-        <v>23</v>
+        <v>19</v>
       </c>
     </row>
     <row r="214" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
@@ -4711,13 +4973,13 @@
         <v>15</v>
       </c>
       <c r="B214" t="s">
-        <v>76</v>
+        <v>61</v>
       </c>
       <c r="C214" s="1">
         <v>46182</v>
       </c>
       <c r="G214" t="s">
-        <v>23</v>
+        <v>19</v>
       </c>
     </row>
     <row r="215" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
@@ -4725,13 +4987,13 @@
         <v>15</v>
       </c>
       <c r="B215" t="s">
-        <v>80</v>
+        <v>65</v>
       </c>
       <c r="C215" s="1">
         <v>46086</v>
       </c>
       <c r="G215" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
     </row>
     <row r="216" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
@@ -4739,13 +5001,13 @@
         <v>15</v>
       </c>
       <c r="B216" t="s">
-        <v>80</v>
+        <v>65</v>
       </c>
       <c r="C216" s="1">
         <v>46087</v>
       </c>
       <c r="G216" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
     </row>
     <row r="217" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
@@ -4753,13 +5015,13 @@
         <v>15</v>
       </c>
       <c r="B217" t="s">
-        <v>80</v>
+        <v>65</v>
       </c>
       <c r="C217" s="1">
         <v>46090</v>
       </c>
       <c r="G217" t="s">
-        <v>23</v>
+        <v>19</v>
       </c>
     </row>
     <row r="218" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
@@ -4767,19 +5029,19 @@
         <v>15</v>
       </c>
       <c r="B218" t="s">
-        <v>80</v>
+        <v>65</v>
       </c>
       <c r="C218" s="1">
         <v>46091</v>
       </c>
       <c r="D218" t="s">
-        <v>77</v>
+        <v>62</v>
       </c>
       <c r="F218" t="s">
-        <v>81</v>
+        <v>66</v>
       </c>
       <c r="G218" t="s">
-        <v>25</v>
+        <v>20</v>
       </c>
     </row>
     <row r="219" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
@@ -4787,13 +5049,13 @@
         <v>15</v>
       </c>
       <c r="B219" t="s">
-        <v>80</v>
+        <v>65</v>
       </c>
       <c r="C219" s="1">
         <v>46092</v>
       </c>
       <c r="G219" t="s">
-        <v>23</v>
+        <v>19</v>
       </c>
     </row>
     <row r="220" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
@@ -4801,13 +5063,13 @@
         <v>15</v>
       </c>
       <c r="B220" t="s">
-        <v>80</v>
+        <v>65</v>
       </c>
       <c r="C220" s="1">
         <v>46093</v>
       </c>
       <c r="G220" t="s">
-        <v>23</v>
+        <v>19</v>
       </c>
     </row>
     <row r="221" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
@@ -4815,22 +5077,22 @@
         <v>15</v>
       </c>
       <c r="B221" t="s">
-        <v>80</v>
+        <v>65</v>
       </c>
       <c r="C221" s="1">
         <v>46094</v>
       </c>
       <c r="D221" t="s">
-        <v>82</v>
+        <v>67</v>
       </c>
       <c r="E221" t="s">
-        <v>82</v>
+        <v>67</v>
       </c>
       <c r="F221" t="s">
-        <v>83</v>
+        <v>68</v>
       </c>
       <c r="G221" t="s">
-        <v>29</v>
+        <v>22</v>
       </c>
     </row>
     <row r="222" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
@@ -4838,13 +5100,13 @@
         <v>15</v>
       </c>
       <c r="B222" t="s">
-        <v>80</v>
+        <v>65</v>
       </c>
       <c r="C222" s="1">
         <v>46097</v>
       </c>
       <c r="G222" t="s">
-        <v>31</v>
+        <v>24</v>
       </c>
     </row>
     <row r="223" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
@@ -4852,13 +5114,13 @@
         <v>15</v>
       </c>
       <c r="B223" t="s">
-        <v>80</v>
+        <v>65</v>
       </c>
       <c r="C223" s="1">
         <v>46098</v>
       </c>
       <c r="G223" t="s">
-        <v>31</v>
+        <v>24</v>
       </c>
     </row>
     <row r="224" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
@@ -4866,13 +5128,13 @@
         <v>15</v>
       </c>
       <c r="B224" t="s">
-        <v>80</v>
+        <v>65</v>
       </c>
       <c r="C224" s="1">
         <v>46099</v>
       </c>
       <c r="G224" t="s">
-        <v>33</v>
+        <v>26</v>
       </c>
     </row>
     <row r="225" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
@@ -4880,13 +5142,13 @@
         <v>15</v>
       </c>
       <c r="B225" t="s">
-        <v>80</v>
+        <v>65</v>
       </c>
       <c r="C225" s="1">
         <v>46100</v>
       </c>
       <c r="G225" t="s">
-        <v>31</v>
+        <v>24</v>
       </c>
     </row>
     <row r="226" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
@@ -4894,22 +5156,22 @@
         <v>15</v>
       </c>
       <c r="B226" t="s">
-        <v>80</v>
+        <v>65</v>
       </c>
       <c r="C226" s="1">
         <v>46101</v>
       </c>
       <c r="D226" t="s">
-        <v>84</v>
+        <v>69</v>
       </c>
       <c r="E226" t="s">
-        <v>84</v>
+        <v>69</v>
       </c>
       <c r="F226" t="s">
-        <v>85</v>
+        <v>70</v>
       </c>
       <c r="G226" t="s">
-        <v>31</v>
+        <v>24</v>
       </c>
     </row>
     <row r="227" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
@@ -4917,13 +5179,13 @@
         <v>15</v>
       </c>
       <c r="B227" t="s">
-        <v>80</v>
+        <v>65</v>
       </c>
       <c r="C227" s="1">
         <v>46104</v>
       </c>
       <c r="G227" t="s">
-        <v>25</v>
+        <v>20</v>
       </c>
     </row>
     <row r="228" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
@@ -4931,13 +5193,13 @@
         <v>15</v>
       </c>
       <c r="B228" t="s">
-        <v>80</v>
+        <v>65</v>
       </c>
       <c r="C228" s="1">
         <v>46105</v>
       </c>
       <c r="G228" t="s">
-        <v>37</v>
+        <v>29</v>
       </c>
     </row>
     <row r="229" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
@@ -4945,13 +5207,13 @@
         <v>15</v>
       </c>
       <c r="B229" t="s">
-        <v>80</v>
+        <v>65</v>
       </c>
       <c r="C229" s="1">
         <v>46106</v>
       </c>
       <c r="G229" t="s">
-        <v>23</v>
+        <v>19</v>
       </c>
     </row>
     <row r="230" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
@@ -4959,13 +5221,13 @@
         <v>15</v>
       </c>
       <c r="B230" t="s">
-        <v>80</v>
+        <v>65</v>
       </c>
       <c r="C230" s="1">
         <v>46107</v>
       </c>
       <c r="G230" t="s">
-        <v>23</v>
+        <v>19</v>
       </c>
     </row>
     <row r="231" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
@@ -4973,13 +5235,13 @@
         <v>15</v>
       </c>
       <c r="B231" t="s">
-        <v>80</v>
+        <v>65</v>
       </c>
       <c r="C231" s="1">
         <v>46108</v>
       </c>
       <c r="G231" t="s">
-        <v>39</v>
+        <v>31</v>
       </c>
     </row>
     <row r="232" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
@@ -4987,16 +5249,16 @@
         <v>15</v>
       </c>
       <c r="B232" t="s">
-        <v>80</v>
+        <v>65</v>
       </c>
       <c r="C232" s="1">
         <v>46111</v>
       </c>
       <c r="F232" t="s">
-        <v>40</v>
+        <v>32</v>
       </c>
       <c r="G232" t="s">
-        <v>41</v>
+        <v>33</v>
       </c>
     </row>
     <row r="233" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
@@ -5004,16 +5266,16 @@
         <v>15</v>
       </c>
       <c r="B233" t="s">
-        <v>80</v>
+        <v>65</v>
       </c>
       <c r="C233" s="1">
         <v>46112</v>
       </c>
       <c r="F233" t="s">
-        <v>40</v>
+        <v>32</v>
       </c>
       <c r="G233" t="s">
-        <v>41</v>
+        <v>33</v>
       </c>
     </row>
     <row r="234" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
@@ -5021,16 +5283,16 @@
         <v>15</v>
       </c>
       <c r="B234" t="s">
-        <v>80</v>
+        <v>65</v>
       </c>
       <c r="C234" s="1">
         <v>46113</v>
       </c>
       <c r="F234" t="s">
-        <v>40</v>
+        <v>32</v>
       </c>
       <c r="G234" t="s">
-        <v>41</v>
+        <v>33</v>
       </c>
     </row>
     <row r="235" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
@@ -5038,16 +5300,16 @@
         <v>15</v>
       </c>
       <c r="B235" t="s">
-        <v>80</v>
+        <v>65</v>
       </c>
       <c r="C235" s="1">
         <v>46114</v>
       </c>
       <c r="F235" t="s">
-        <v>40</v>
+        <v>32</v>
       </c>
       <c r="G235" t="s">
-        <v>41</v>
+        <v>33</v>
       </c>
     </row>
     <row r="236" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
@@ -5055,16 +5317,16 @@
         <v>15</v>
       </c>
       <c r="B236" t="s">
-        <v>80</v>
+        <v>65</v>
       </c>
       <c r="C236" s="1">
         <v>46115</v>
       </c>
       <c r="F236" t="s">
-        <v>40</v>
+        <v>32</v>
       </c>
       <c r="G236" t="s">
-        <v>41</v>
+        <v>33</v>
       </c>
     </row>
     <row r="237" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
@@ -5072,13 +5334,13 @@
         <v>15</v>
       </c>
       <c r="B237" t="s">
-        <v>80</v>
+        <v>65</v>
       </c>
       <c r="C237" s="1">
         <v>46118</v>
       </c>
       <c r="G237" t="s">
-        <v>44</v>
+        <v>35</v>
       </c>
     </row>
     <row r="238" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
@@ -5086,13 +5348,13 @@
         <v>15</v>
       </c>
       <c r="B238" t="s">
-        <v>80</v>
+        <v>65</v>
       </c>
       <c r="C238" s="1">
         <v>46119</v>
       </c>
       <c r="G238" t="s">
-        <v>23</v>
+        <v>19</v>
       </c>
     </row>
     <row r="239" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
@@ -5100,13 +5362,13 @@
         <v>15</v>
       </c>
       <c r="B239" t="s">
-        <v>80</v>
+        <v>65</v>
       </c>
       <c r="C239" s="1">
         <v>46120</v>
       </c>
       <c r="G239" t="s">
-        <v>45</v>
+        <v>36</v>
       </c>
     </row>
     <row r="240" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
@@ -5114,13 +5376,13 @@
         <v>15</v>
       </c>
       <c r="B240" t="s">
-        <v>80</v>
+        <v>65</v>
       </c>
       <c r="C240" s="1">
         <v>46121</v>
       </c>
       <c r="G240" t="s">
-        <v>23</v>
+        <v>19</v>
       </c>
     </row>
     <row r="241" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
@@ -5128,13 +5390,13 @@
         <v>15</v>
       </c>
       <c r="B241" t="s">
-        <v>80</v>
+        <v>65</v>
       </c>
       <c r="C241" s="1">
         <v>46122</v>
       </c>
       <c r="G241" t="s">
-        <v>23</v>
+        <v>19</v>
       </c>
     </row>
     <row r="242" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
@@ -5142,13 +5404,13 @@
         <v>15</v>
       </c>
       <c r="B242" t="s">
-        <v>80</v>
+        <v>65</v>
       </c>
       <c r="C242" s="1">
         <v>46125</v>
       </c>
       <c r="G242" t="s">
-        <v>23</v>
+        <v>19</v>
       </c>
     </row>
     <row r="243" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
@@ -5156,13 +5418,13 @@
         <v>15</v>
       </c>
       <c r="B243" t="s">
-        <v>80</v>
+        <v>65</v>
       </c>
       <c r="C243" s="1">
         <v>46126</v>
       </c>
       <c r="G243" t="s">
-        <v>23</v>
+        <v>19</v>
       </c>
     </row>
     <row r="244" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
@@ -5170,13 +5432,13 @@
         <v>15</v>
       </c>
       <c r="B244" t="s">
-        <v>80</v>
+        <v>65</v>
       </c>
       <c r="C244" s="1">
         <v>46127</v>
       </c>
       <c r="G244" t="s">
-        <v>23</v>
+        <v>19</v>
       </c>
     </row>
     <row r="245" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
@@ -5184,16 +5446,16 @@
         <v>15</v>
       </c>
       <c r="B245" t="s">
-        <v>80</v>
+        <v>65</v>
       </c>
       <c r="C245" s="1">
         <v>46128</v>
       </c>
       <c r="F245" t="s">
-        <v>47</v>
+        <v>37</v>
       </c>
       <c r="G245" t="s">
-        <v>23</v>
+        <v>19</v>
       </c>
     </row>
     <row r="246" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
@@ -5201,16 +5463,16 @@
         <v>15</v>
       </c>
       <c r="B246" t="s">
-        <v>80</v>
+        <v>65</v>
       </c>
       <c r="C246" s="1">
         <v>46129</v>
       </c>
       <c r="F246" t="s">
-        <v>48</v>
+        <v>38</v>
       </c>
       <c r="G246" t="s">
-        <v>49</v>
+        <v>39</v>
       </c>
     </row>
     <row r="247" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
@@ -5218,13 +5480,13 @@
         <v>15</v>
       </c>
       <c r="B247" t="s">
-        <v>80</v>
+        <v>65</v>
       </c>
       <c r="C247" s="1">
         <v>46132</v>
       </c>
       <c r="G247" t="s">
-        <v>23</v>
+        <v>19</v>
       </c>
     </row>
     <row r="248" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
@@ -5232,13 +5494,13 @@
         <v>15</v>
       </c>
       <c r="B248" t="s">
-        <v>80</v>
+        <v>65</v>
       </c>
       <c r="C248" s="1">
         <v>46133</v>
       </c>
       <c r="G248" t="s">
-        <v>23</v>
+        <v>19</v>
       </c>
     </row>
     <row r="249" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
@@ -5246,13 +5508,13 @@
         <v>15</v>
       </c>
       <c r="B249" t="s">
-        <v>80</v>
+        <v>65</v>
       </c>
       <c r="C249" s="1">
         <v>46134</v>
       </c>
       <c r="G249" t="s">
-        <v>23</v>
+        <v>19</v>
       </c>
     </row>
     <row r="250" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
@@ -5260,13 +5522,13 @@
         <v>15</v>
       </c>
       <c r="B250" t="s">
-        <v>80</v>
+        <v>65</v>
       </c>
       <c r="C250" s="1">
         <v>46135</v>
       </c>
       <c r="G250" t="s">
-        <v>23</v>
+        <v>19</v>
       </c>
     </row>
     <row r="251" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
@@ -5274,13 +5536,13 @@
         <v>15</v>
       </c>
       <c r="B251" t="s">
-        <v>80</v>
+        <v>65</v>
       </c>
       <c r="C251" s="1">
         <v>46136</v>
       </c>
       <c r="G251" t="s">
-        <v>23</v>
+        <v>19</v>
       </c>
     </row>
     <row r="252" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
@@ -5288,13 +5550,13 @@
         <v>15</v>
       </c>
       <c r="B252" t="s">
-        <v>80</v>
+        <v>65</v>
       </c>
       <c r="C252" s="1">
         <v>46139</v>
       </c>
       <c r="G252" t="s">
-        <v>23</v>
+        <v>19</v>
       </c>
     </row>
     <row r="253" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
@@ -5302,13 +5564,13 @@
         <v>15</v>
       </c>
       <c r="B253" t="s">
-        <v>80</v>
+        <v>65</v>
       </c>
       <c r="C253" s="1">
         <v>46140</v>
       </c>
       <c r="G253" t="s">
-        <v>23</v>
+        <v>19</v>
       </c>
     </row>
     <row r="254" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
@@ -5316,13 +5578,13 @@
         <v>15</v>
       </c>
       <c r="B254" t="s">
-        <v>80</v>
+        <v>65</v>
       </c>
       <c r="C254" s="1">
         <v>46141</v>
       </c>
       <c r="G254" t="s">
-        <v>23</v>
+        <v>19</v>
       </c>
     </row>
     <row r="255" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
@@ -5330,13 +5592,13 @@
         <v>15</v>
       </c>
       <c r="B255" t="s">
-        <v>80</v>
+        <v>65</v>
       </c>
       <c r="C255" s="1">
         <v>46142</v>
       </c>
       <c r="G255" t="s">
-        <v>23</v>
+        <v>19</v>
       </c>
     </row>
     <row r="256" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
@@ -5344,13 +5606,13 @@
         <v>15</v>
       </c>
       <c r="B256" t="s">
-        <v>80</v>
+        <v>65</v>
       </c>
       <c r="C256" s="1">
         <v>46143</v>
       </c>
       <c r="G256" t="s">
-        <v>73</v>
+        <v>58</v>
       </c>
     </row>
     <row r="257" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
@@ -5358,13 +5620,13 @@
         <v>15</v>
       </c>
       <c r="B257" t="s">
-        <v>80</v>
+        <v>65</v>
       </c>
       <c r="C257" s="1">
         <v>46146</v>
       </c>
       <c r="G257" t="s">
-        <v>23</v>
+        <v>19</v>
       </c>
     </row>
     <row r="258" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
@@ -5372,13 +5634,13 @@
         <v>15</v>
       </c>
       <c r="B258" t="s">
-        <v>80</v>
+        <v>65</v>
       </c>
       <c r="C258" s="1">
         <v>46147</v>
       </c>
       <c r="G258" t="s">
-        <v>52</v>
+        <v>42</v>
       </c>
     </row>
     <row r="259" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
@@ -5386,13 +5648,13 @@
         <v>15</v>
       </c>
       <c r="B259" t="s">
-        <v>80</v>
+        <v>65</v>
       </c>
       <c r="C259" s="1">
         <v>46148</v>
       </c>
       <c r="G259" t="s">
-        <v>23</v>
+        <v>19</v>
       </c>
     </row>
     <row r="260" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
@@ -5400,13 +5662,13 @@
         <v>15</v>
       </c>
       <c r="B260" t="s">
-        <v>80</v>
+        <v>65</v>
       </c>
       <c r="C260" s="1">
         <v>46149</v>
       </c>
       <c r="G260" t="s">
-        <v>23</v>
+        <v>19</v>
       </c>
     </row>
     <row r="261" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
@@ -5414,13 +5676,13 @@
         <v>15</v>
       </c>
       <c r="B261" t="s">
-        <v>80</v>
+        <v>65</v>
       </c>
       <c r="C261" s="1">
         <v>46150</v>
       </c>
       <c r="G261" t="s">
-        <v>74</v>
+        <v>59</v>
       </c>
     </row>
     <row r="262" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
@@ -5428,13 +5690,13 @@
         <v>15</v>
       </c>
       <c r="B262" t="s">
-        <v>80</v>
+        <v>65</v>
       </c>
       <c r="C262" s="1">
         <v>46153</v>
       </c>
       <c r="G262" t="s">
-        <v>23</v>
+        <v>19</v>
       </c>
     </row>
     <row r="263" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
@@ -5442,13 +5704,13 @@
         <v>15</v>
       </c>
       <c r="B263" t="s">
-        <v>80</v>
+        <v>65</v>
       </c>
       <c r="C263" s="1">
         <v>46154</v>
       </c>
       <c r="G263" t="s">
-        <v>23</v>
+        <v>19</v>
       </c>
     </row>
     <row r="264" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
@@ -5456,13 +5718,13 @@
         <v>15</v>
       </c>
       <c r="B264" t="s">
-        <v>80</v>
+        <v>65</v>
       </c>
       <c r="C264" s="1">
         <v>46155</v>
       </c>
       <c r="G264" t="s">
-        <v>23</v>
+        <v>19</v>
       </c>
     </row>
     <row r="265" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
@@ -5470,13 +5732,13 @@
         <v>15</v>
       </c>
       <c r="B265" t="s">
-        <v>80</v>
+        <v>65</v>
       </c>
       <c r="C265" s="1">
         <v>46156</v>
       </c>
       <c r="G265" t="s">
-        <v>23</v>
+        <v>19</v>
       </c>
     </row>
     <row r="266" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
@@ -5484,13 +5746,13 @@
         <v>15</v>
       </c>
       <c r="B266" t="s">
-        <v>80</v>
+        <v>65</v>
       </c>
       <c r="C266" s="1">
         <v>46157</v>
       </c>
       <c r="G266" t="s">
-        <v>23</v>
+        <v>19</v>
       </c>
     </row>
     <row r="267" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
@@ -5498,13 +5760,13 @@
         <v>15</v>
       </c>
       <c r="B267" t="s">
-        <v>80</v>
+        <v>65</v>
       </c>
       <c r="C267" s="1">
         <v>46160</v>
       </c>
       <c r="G267" t="s">
-        <v>23</v>
+        <v>19</v>
       </c>
     </row>
     <row r="268" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
@@ -5512,13 +5774,13 @@
         <v>15</v>
       </c>
       <c r="B268" t="s">
-        <v>80</v>
+        <v>65</v>
       </c>
       <c r="C268" s="1">
         <v>46161</v>
       </c>
       <c r="G268" t="s">
-        <v>23</v>
+        <v>19</v>
       </c>
     </row>
     <row r="269" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
@@ -5526,13 +5788,13 @@
         <v>15</v>
       </c>
       <c r="B269" t="s">
-        <v>80</v>
+        <v>65</v>
       </c>
       <c r="C269" s="1">
         <v>46162</v>
       </c>
       <c r="G269" t="s">
-        <v>23</v>
+        <v>19</v>
       </c>
     </row>
     <row r="270" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
@@ -5540,13 +5802,13 @@
         <v>15</v>
       </c>
       <c r="B270" t="s">
-        <v>80</v>
+        <v>65</v>
       </c>
       <c r="C270" s="1">
         <v>46163</v>
       </c>
       <c r="G270" t="s">
-        <v>23</v>
+        <v>19</v>
       </c>
     </row>
     <row r="271" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
@@ -5554,16 +5816,16 @@
         <v>15</v>
       </c>
       <c r="B271" t="s">
-        <v>80</v>
+        <v>65</v>
       </c>
       <c r="C271" s="1">
         <v>46164</v>
       </c>
       <c r="F271" t="s">
-        <v>53</v>
+        <v>43</v>
       </c>
       <c r="G271" t="s">
-        <v>23</v>
+        <v>19</v>
       </c>
     </row>
     <row r="272" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
@@ -5571,16 +5833,16 @@
         <v>15</v>
       </c>
       <c r="B272" t="s">
-        <v>80</v>
+        <v>65</v>
       </c>
       <c r="C272" s="1">
         <v>46167</v>
       </c>
       <c r="F272" t="s">
-        <v>54</v>
+        <v>44</v>
       </c>
       <c r="G272" t="s">
-        <v>55</v>
+        <v>45</v>
       </c>
     </row>
     <row r="273" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
@@ -5588,13 +5850,13 @@
         <v>15</v>
       </c>
       <c r="B273" t="s">
-        <v>80</v>
+        <v>65</v>
       </c>
       <c r="C273" s="1">
         <v>46168</v>
       </c>
       <c r="G273" t="s">
-        <v>23</v>
+        <v>19</v>
       </c>
     </row>
     <row r="274" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
@@ -5602,13 +5864,13 @@
         <v>15</v>
       </c>
       <c r="B274" t="s">
-        <v>80</v>
+        <v>65</v>
       </c>
       <c r="C274" s="1">
         <v>46169</v>
       </c>
       <c r="G274" t="s">
-        <v>23</v>
+        <v>19</v>
       </c>
     </row>
     <row r="275" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
@@ -5616,13 +5878,13 @@
         <v>15</v>
       </c>
       <c r="B275" t="s">
-        <v>80</v>
+        <v>65</v>
       </c>
       <c r="C275" s="1">
         <v>46170</v>
       </c>
       <c r="G275" t="s">
-        <v>23</v>
+        <v>19</v>
       </c>
     </row>
     <row r="276" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
@@ -5630,13 +5892,13 @@
         <v>15</v>
       </c>
       <c r="B276" t="s">
-        <v>80</v>
+        <v>65</v>
       </c>
       <c r="C276" s="1">
         <v>46171</v>
       </c>
       <c r="G276" t="s">
-        <v>74</v>
+        <v>59</v>
       </c>
     </row>
     <row r="277" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
@@ -5644,13 +5906,13 @@
         <v>15</v>
       </c>
       <c r="B277" t="s">
-        <v>80</v>
+        <v>65</v>
       </c>
       <c r="C277" s="1">
         <v>46174</v>
       </c>
       <c r="G277" t="s">
-        <v>23</v>
+        <v>19</v>
       </c>
     </row>
     <row r="278" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
@@ -5658,13 +5920,13 @@
         <v>15</v>
       </c>
       <c r="B278" t="s">
-        <v>80</v>
+        <v>65</v>
       </c>
       <c r="C278" s="1">
         <v>46175</v>
       </c>
       <c r="G278" t="s">
-        <v>23</v>
+        <v>19</v>
       </c>
     </row>
     <row r="279" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
@@ -5672,13 +5934,13 @@
         <v>15</v>
       </c>
       <c r="B279" t="s">
-        <v>80</v>
+        <v>65</v>
       </c>
       <c r="C279" s="1">
         <v>46176</v>
       </c>
       <c r="G279" t="s">
-        <v>23</v>
+        <v>19</v>
       </c>
     </row>
     <row r="280" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
@@ -5686,13 +5948,13 @@
         <v>15</v>
       </c>
       <c r="B280" t="s">
-        <v>80</v>
+        <v>65</v>
       </c>
       <c r="C280" s="1">
         <v>46177</v>
       </c>
       <c r="G280" t="s">
-        <v>23</v>
+        <v>19</v>
       </c>
     </row>
     <row r="281" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
@@ -5700,13 +5962,13 @@
         <v>15</v>
       </c>
       <c r="B281" t="s">
-        <v>80</v>
+        <v>65</v>
       </c>
       <c r="C281" s="1">
         <v>46178</v>
       </c>
       <c r="G281" t="s">
-        <v>75</v>
+        <v>60</v>
       </c>
     </row>
     <row r="282" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
@@ -5714,13 +5976,13 @@
         <v>15</v>
       </c>
       <c r="B282" t="s">
-        <v>80</v>
+        <v>65</v>
       </c>
       <c r="C282" s="1">
         <v>46181</v>
       </c>
       <c r="G282" t="s">
-        <v>23</v>
+        <v>19</v>
       </c>
     </row>
     <row r="283" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
@@ -5728,13 +5990,13 @@
         <v>15</v>
       </c>
       <c r="B283" t="s">
-        <v>80</v>
+        <v>65</v>
       </c>
       <c r="C283" s="1">
         <v>46182</v>
       </c>
       <c r="G283" t="s">
-        <v>23</v>
+        <v>19</v>
       </c>
     </row>
   </sheetData>
@@ -5747,5 +6009,6 @@
     </filterColumn>
   </autoFilter>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" r:id="rId1"/>
 </worksheet>
 </file>
--- a/Pacing_Dates_Master.xlsx
+++ b/Pacing_Dates_Master.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\github\GCI\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:9_{A4655B58-D611-4107-868E-04DB1A558A19}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EF452411-42C2-4979-AF9B-298592F22B83}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="23260" windowHeight="14860" xr2:uid="{327FF7BE-3859-42FE-861D-17B3CC93C4A1}"/>
   </bookViews>
@@ -23,7 +23,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1187" uniqueCount="115">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1231" uniqueCount="126">
   <si>
     <t>SourceType</t>
   </si>
@@ -324,9 +324,6 @@
     <t>PCEP Certification</t>
   </si>
   <si>
-    <t>Design Thinking</t>
-  </si>
-  <si>
     <t>Virtual Assignment</t>
   </si>
   <si>
@@ -348,38 +345,75 @@
     <t>All hardware classes</t>
   </si>
   <si>
-    <t>All hardware classes (2nd session)</t>
-  </si>
-  <si>
     <t>AP Computer Science A: Game Design</t>
   </si>
   <si>
-    <t>3rd session AP Computer Science A</t>
-  </si>
-  <si>
-    <t>Website Checkpoint 1</t>
-  </si>
-  <si>
     <t>AP Computer Science A milestone</t>
   </si>
   <si>
     <t>AP Computer Science A final website due</t>
   </si>
   <si>
-    <t>Website Checkpoint 2</t>
-  </si>
-  <si>
     <t>AP Exam</t>
   </si>
   <si>
     <t>Deadline for submissions for MP3</t>
+  </si>
+  <si>
+    <t>IT Specialist Certification - Python Practice Test</t>
+  </si>
+  <si>
+    <t>Three Keys - QA Project</t>
+  </si>
+  <si>
+    <t>5.4: Forensic Case 3: Exif Data</t>
+  </si>
+  <si>
+    <t>Catch up/Brain Break</t>
+  </si>
+  <si>
+    <t>Teamwork Assignment Due - Catch up/Brain Break</t>
+  </si>
+  <si>
+    <t>9.1: Identifying Risks</t>
+  </si>
+  <si>
+    <t>9.2: Assessing Risks</t>
+  </si>
+  <si>
+    <t>9.3: Risk Response</t>
+  </si>
+  <si>
+    <t>9.4: Penetration Testing</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> 9.5: Risk Management Quiz</t>
+  </si>
+  <si>
+    <t>Base Camp: Teamwork Assignment Due</t>
+  </si>
+  <si>
+    <t>Game Dev: Release Your Game</t>
+  </si>
+  <si>
+    <t>AP: Data Collections Due</t>
+  </si>
+  <si>
+    <t>Web Dev: Website Checkpoint 1
+Game Dev: Explore the Industry</t>
+  </si>
+  <si>
+    <t>Web Dev: Website Checkpoint 2</t>
+  </si>
+  <si>
+    <t>AP: Exam Prep</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="18" x14ac:knownFonts="1">
+  <fonts count="19" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -513,6 +547,12 @@
       <name val="Aptos Narrow"/>
       <family val="2"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="8"/>
+      <color rgb="FF555555"/>
+      <name val="Arial"/>
+      <family val="2"/>
     </font>
   </fonts>
   <fills count="33">
@@ -856,12 +896,13 @@
     <xf numFmtId="0" fontId="1" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="1" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="42">
     <cellStyle name="20% - Accent1" xfId="19" builtinId="30" customBuiltin="1"/>
@@ -1237,6 +1278,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3048F481-4A4B-498D-A291-01B119D1D7C2}">
+  <sheetPr filterMode="1"/>
   <dimension ref="A1:I277"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
@@ -1278,7 +1320,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="2" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
       <c r="A2" t="s">
         <v>9</v>
       </c>
@@ -1301,7 +1343,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="3" spans="1:9" ht="29" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:9" ht="29" hidden="1" x14ac:dyDescent="0.35">
       <c r="A3" t="s">
         <v>9</v>
       </c>
@@ -1324,7 +1366,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="4" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
       <c r="A4" t="s">
         <v>9</v>
       </c>
@@ -1347,7 +1389,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="5" spans="1:9" ht="29" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:9" ht="29" hidden="1" x14ac:dyDescent="0.35">
       <c r="A5" t="s">
         <v>9</v>
       </c>
@@ -1370,7 +1412,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="6" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
       <c r="A6" t="s">
         <v>9</v>
       </c>
@@ -1393,7 +1435,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="7" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
       <c r="A7" t="s">
         <v>9</v>
       </c>
@@ -1416,7 +1458,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="8" spans="1:9" ht="43.5" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:9" ht="43.5" hidden="1" x14ac:dyDescent="0.35">
       <c r="A8" t="s">
         <v>9</v>
       </c>
@@ -1439,7 +1481,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="9" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="9" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
       <c r="A9" t="s">
         <v>9</v>
       </c>
@@ -1465,7 +1507,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="10" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="10" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
       <c r="A10" t="s">
         <v>9</v>
       </c>
@@ -1488,7 +1530,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="11" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="11" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
       <c r="A11" t="s">
         <v>9</v>
       </c>
@@ -1514,7 +1556,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="12" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="12" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
       <c r="A12" t="s">
         <v>9</v>
       </c>
@@ -1537,7 +1579,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="13" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="13" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
       <c r="A13" t="s">
         <v>9</v>
       </c>
@@ -1560,7 +1602,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="14" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="14" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
       <c r="A14" t="s">
         <v>9</v>
       </c>
@@ -1583,7 +1625,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="15" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="15" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
       <c r="A15" t="s">
         <v>9</v>
       </c>
@@ -1606,7 +1648,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="16" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="16" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
       <c r="A16" t="s">
         <v>9</v>
       </c>
@@ -1629,7 +1671,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="17" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="17" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
       <c r="A17" t="s">
         <v>9</v>
       </c>
@@ -1652,7 +1694,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="18" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="18" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
       <c r="A18" t="s">
         <v>9</v>
       </c>
@@ -1675,7 +1717,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="19" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="19" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
       <c r="A19" t="s">
         <v>9</v>
       </c>
@@ -1698,7 +1740,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="20" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="20" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
       <c r="A20" t="s">
         <v>9</v>
       </c>
@@ -1721,7 +1763,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="21" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="21" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
       <c r="A21" t="s">
         <v>9</v>
       </c>
@@ -1744,7 +1786,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="22" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="22" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
       <c r="A22" t="s">
         <v>9</v>
       </c>
@@ -1767,7 +1809,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="23" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="23" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
       <c r="A23" t="s">
         <v>9</v>
       </c>
@@ -1790,7 +1832,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="24" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="24" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
       <c r="A24" t="s">
         <v>9</v>
       </c>
@@ -1810,7 +1852,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="25" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="25" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
       <c r="A25" t="s">
         <v>9</v>
       </c>
@@ -1830,7 +1872,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="26" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="26" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
       <c r="A26" t="s">
         <v>9</v>
       </c>
@@ -1850,7 +1892,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="27" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="27" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
       <c r="A27" t="s">
         <v>9</v>
       </c>
@@ -1870,7 +1912,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="28" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="28" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
       <c r="A28" t="s">
         <v>9</v>
       </c>
@@ -1890,7 +1932,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="29" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="29" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
       <c r="A29" t="s">
         <v>9</v>
       </c>
@@ -1910,7 +1952,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="30" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="30" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
       <c r="A30" t="s">
         <v>9</v>
       </c>
@@ -1930,7 +1972,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="31" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="31" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
       <c r="A31" t="s">
         <v>9</v>
       </c>
@@ -1950,7 +1992,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="32" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="32" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
       <c r="A32" t="s">
         <v>9</v>
       </c>
@@ -1973,7 +2015,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="33" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="33" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
       <c r="A33" t="s">
         <v>9</v>
       </c>
@@ -1996,7 +2038,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="34" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="34" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
       <c r="A34" t="s">
         <v>9</v>
       </c>
@@ -2019,7 +2061,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="35" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="35" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
       <c r="A35" t="s">
         <v>9</v>
       </c>
@@ -2042,7 +2084,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="36" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="36" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
       <c r="A36" t="s">
         <v>9</v>
       </c>
@@ -2062,7 +2104,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="37" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="37" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
       <c r="A37" t="s">
         <v>9</v>
       </c>
@@ -2082,7 +2124,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="38" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="38" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
       <c r="A38" t="s">
         <v>9</v>
       </c>
@@ -2102,7 +2144,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="39" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="39" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
       <c r="A39" t="s">
         <v>9</v>
       </c>
@@ -2122,7 +2164,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="40" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="40" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
       <c r="A40" t="s">
         <v>9</v>
       </c>
@@ -2142,7 +2184,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="41" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="41" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
       <c r="A41" t="s">
         <v>9</v>
       </c>
@@ -2162,7 +2204,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="42" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="42" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
       <c r="A42" t="s">
         <v>9</v>
       </c>
@@ -2182,7 +2224,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="43" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="43" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
       <c r="A43" t="s">
         <v>9</v>
       </c>
@@ -2202,7 +2244,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="44" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="44" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
       <c r="A44" t="s">
         <v>9</v>
       </c>
@@ -2222,7 +2264,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="45" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="45" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
       <c r="A45" t="s">
         <v>9</v>
       </c>
@@ -2242,7 +2284,7 @@
         <v>63</v>
       </c>
     </row>
-    <row r="46" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="46" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
       <c r="A46" t="s">
         <v>9</v>
       </c>
@@ -2262,7 +2304,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="47" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="47" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
       <c r="A47" t="s">
         <v>9</v>
       </c>
@@ -2282,7 +2324,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="48" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="48" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
       <c r="A48" t="s">
         <v>9</v>
       </c>
@@ -2302,7 +2344,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="49" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="49" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
       <c r="A49" t="s">
         <v>9</v>
       </c>
@@ -2322,7 +2364,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="50" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="50" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
       <c r="A50" t="s">
         <v>9</v>
       </c>
@@ -2342,7 +2384,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="51" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="51" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
       <c r="A51" t="s">
         <v>9</v>
       </c>
@@ -2362,7 +2404,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="52" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="52" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
       <c r="A52" t="s">
         <v>9</v>
       </c>
@@ -2382,7 +2424,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="53" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="53" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
       <c r="A53" t="s">
         <v>9</v>
       </c>
@@ -2402,7 +2444,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="54" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="54" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
       <c r="A54" t="s">
         <v>9</v>
       </c>
@@ -2422,7 +2464,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="55" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="55" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
       <c r="A55" t="s">
         <v>9</v>
       </c>
@@ -2442,7 +2484,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="56" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="56" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
       <c r="A56" t="s">
         <v>9</v>
       </c>
@@ -2462,7 +2504,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="57" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="57" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
       <c r="A57" t="s">
         <v>9</v>
       </c>
@@ -2482,7 +2524,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="58" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="58" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
       <c r="A58" t="s">
         <v>9</v>
       </c>
@@ -2505,7 +2547,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="59" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="59" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
       <c r="A59" t="s">
         <v>9</v>
       </c>
@@ -2528,7 +2570,7 @@
         <v>72</v>
       </c>
     </row>
-    <row r="60" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="60" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
       <c r="A60" t="s">
         <v>9</v>
       </c>
@@ -2548,7 +2590,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="61" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="61" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
       <c r="A61" t="s">
         <v>9</v>
       </c>
@@ -2568,7 +2610,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="62" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="62" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
       <c r="A62" t="s">
         <v>9</v>
       </c>
@@ -2588,7 +2630,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="63" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="63" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
       <c r="A63" t="s">
         <v>9</v>
       </c>
@@ -2608,7 +2650,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="64" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="64" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
       <c r="A64" t="s">
         <v>9</v>
       </c>
@@ -2628,7 +2670,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="65" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="65" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
       <c r="A65" t="s">
         <v>9</v>
       </c>
@@ -2648,7 +2690,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="66" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="66" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
       <c r="A66" t="s">
         <v>9</v>
       </c>
@@ -2668,7 +2710,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="67" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="67" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
       <c r="A67" t="s">
         <v>9</v>
       </c>
@@ -2688,7 +2730,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="68" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="68" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
       <c r="A68" t="s">
         <v>9</v>
       </c>
@@ -2708,7 +2750,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="69" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="69" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
       <c r="A69" t="s">
         <v>9</v>
       </c>
@@ -2728,7 +2770,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="70" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="70" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
       <c r="A70" t="s">
         <v>9</v>
       </c>
@@ -2748,7 +2790,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="71" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="71" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
       <c r="A71" t="s">
         <v>9</v>
       </c>
@@ -2771,7 +2813,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="72" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="72" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
       <c r="A72" t="s">
         <v>9</v>
       </c>
@@ -2794,7 +2836,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="73" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="73" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
       <c r="A73" t="s">
         <v>9</v>
       </c>
@@ -2820,7 +2862,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="74" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="74" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
       <c r="A74" t="s">
         <v>9</v>
       </c>
@@ -2843,7 +2885,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="75" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="75" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
       <c r="A75" t="s">
         <v>9</v>
       </c>
@@ -2866,7 +2908,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="76" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="76" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
       <c r="A76" t="s">
         <v>9</v>
       </c>
@@ -2889,7 +2931,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="77" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="77" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
       <c r="A77" t="s">
         <v>9</v>
       </c>
@@ -2912,7 +2954,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="78" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="78" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
       <c r="A78" t="s">
         <v>9</v>
       </c>
@@ -2938,7 +2980,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="79" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="79" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
       <c r="A79" t="s">
         <v>9</v>
       </c>
@@ -2961,7 +3003,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="80" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="80" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
       <c r="A80" t="s">
         <v>9</v>
       </c>
@@ -2987,7 +3029,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="81" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="81" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
       <c r="A81" t="s">
         <v>9</v>
       </c>
@@ -3010,7 +3052,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="82" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="82" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
       <c r="A82" t="s">
         <v>9</v>
       </c>
@@ -3024,7 +3066,7 @@
         <v>88</v>
       </c>
       <c r="E82" t="s">
-        <v>88</v>
+        <v>86</v>
       </c>
       <c r="F82" t="s">
         <v>91</v>
@@ -3033,7 +3075,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="83" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="83" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
       <c r="A83" t="s">
         <v>9</v>
       </c>
@@ -3056,7 +3098,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="84" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="84" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
       <c r="A84" t="s">
         <v>9</v>
       </c>
@@ -3079,7 +3121,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="85" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="85" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
       <c r="A85" t="s">
         <v>9</v>
       </c>
@@ -3102,7 +3144,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="86" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="86" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
       <c r="A86" t="s">
         <v>9</v>
       </c>
@@ -3125,7 +3167,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="87" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="87" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
       <c r="A87" t="s">
         <v>9</v>
       </c>
@@ -3148,7 +3190,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="88" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="88" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
       <c r="A88" t="s">
         <v>9</v>
       </c>
@@ -3171,7 +3213,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="89" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="89" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
       <c r="A89" t="s">
         <v>9</v>
       </c>
@@ -3194,7 +3236,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="90" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="90" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
       <c r="A90" t="s">
         <v>9</v>
       </c>
@@ -3217,7 +3259,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="91" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="91" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
       <c r="A91" t="s">
         <v>9</v>
       </c>
@@ -3240,7 +3282,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="92" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="92" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
       <c r="A92" t="s">
         <v>9</v>
       </c>
@@ -3263,7 +3305,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="93" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="93" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
       <c r="A93" t="s">
         <v>9</v>
       </c>
@@ -3283,7 +3325,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="94" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="94" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
       <c r="A94" t="s">
         <v>9</v>
       </c>
@@ -3294,7 +3336,7 @@
         <v>46119</v>
       </c>
       <c r="D94" t="s">
-        <v>95</v>
+        <v>110</v>
       </c>
       <c r="E94" t="s">
         <v>88</v>
@@ -3303,7 +3345,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="95" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="95" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
       <c r="A95" t="s">
         <v>9</v>
       </c>
@@ -3314,7 +3356,7 @@
         <v>46120</v>
       </c>
       <c r="D95" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="E95" t="s">
         <v>88</v>
@@ -3323,7 +3365,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="96" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="96" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
       <c r="A96" t="s">
         <v>9</v>
       </c>
@@ -3343,7 +3385,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="97" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="97" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
       <c r="A97" t="s">
         <v>9</v>
       </c>
@@ -3354,16 +3396,16 @@
         <v>46122</v>
       </c>
       <c r="D97" t="s">
-        <v>97</v>
+        <v>111</v>
       </c>
       <c r="E97" t="s">
-        <v>95</v>
+        <v>111</v>
       </c>
       <c r="H97" t="s">
         <v>15</v>
       </c>
     </row>
-    <row r="98" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="98" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
       <c r="A98" t="s">
         <v>9</v>
       </c>
@@ -3374,16 +3416,16 @@
         <v>46125</v>
       </c>
       <c r="D98" t="s">
-        <v>98</v>
+        <v>96</v>
       </c>
       <c r="E98" t="s">
-        <v>96</v>
+        <v>110</v>
       </c>
       <c r="H98" t="s">
         <v>15</v>
       </c>
     </row>
-    <row r="99" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="99" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
       <c r="A99" t="s">
         <v>9</v>
       </c>
@@ -3394,16 +3436,16 @@
         <v>46126</v>
       </c>
       <c r="D99" t="s">
-        <v>98</v>
+        <v>96</v>
       </c>
       <c r="E99" t="s">
-        <v>97</v>
+        <v>95</v>
       </c>
       <c r="H99" t="s">
         <v>15</v>
       </c>
     </row>
-    <row r="100" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="100" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
       <c r="A100" t="s">
         <v>9</v>
       </c>
@@ -3414,16 +3456,13 @@
         <v>46127</v>
       </c>
       <c r="D100" t="s">
-        <v>98</v>
-      </c>
-      <c r="E100" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="H100" t="s">
         <v>15</v>
       </c>
     </row>
-    <row r="101" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="101" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
       <c r="A101" t="s">
         <v>9</v>
       </c>
@@ -3446,7 +3485,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="102" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="102" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
       <c r="A102" t="s">
         <v>9</v>
       </c>
@@ -3457,10 +3496,10 @@
         <v>46129</v>
       </c>
       <c r="D102" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="E102" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="G102" t="s">
         <v>49</v>
@@ -3469,7 +3508,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="103" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="103" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
       <c r="A103" t="s">
         <v>9</v>
       </c>
@@ -3479,9 +3518,6 @@
       <c r="C103" s="1">
         <v>46132</v>
       </c>
-      <c r="D103" t="s">
-        <v>98</v>
-      </c>
       <c r="E103" t="s">
         <v>14</v>
       </c>
@@ -3489,7 +3525,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="104" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="104" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
       <c r="A104" t="s">
         <v>9</v>
       </c>
@@ -3499,17 +3535,14 @@
       <c r="C104" s="1">
         <v>46133</v>
       </c>
-      <c r="D104" t="s">
-        <v>98</v>
-      </c>
       <c r="E104" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="H104" t="s">
         <v>15</v>
       </c>
     </row>
-    <row r="105" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="105" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
       <c r="A105" t="s">
         <v>9</v>
       </c>
@@ -3523,13 +3556,13 @@
         <v>38</v>
       </c>
       <c r="E105" t="s">
-        <v>98</v>
+        <v>96</v>
       </c>
       <c r="H105" t="s">
         <v>15</v>
       </c>
     </row>
-    <row r="106" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="106" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
       <c r="A106" t="s">
         <v>9</v>
       </c>
@@ -3543,13 +3576,13 @@
         <v>38</v>
       </c>
       <c r="E106" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="H106" t="s">
         <v>15</v>
       </c>
     </row>
-    <row r="107" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="107" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
       <c r="A107" t="s">
         <v>9</v>
       </c>
@@ -3560,16 +3593,16 @@
         <v>46136</v>
       </c>
       <c r="D107" t="s">
-        <v>38</v>
+        <v>111</v>
       </c>
       <c r="E107" t="s">
-        <v>98</v>
+        <v>111</v>
       </c>
       <c r="H107" t="s">
         <v>15</v>
       </c>
     </row>
-    <row r="108" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="108" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
       <c r="A108" t="s">
         <v>9</v>
       </c>
@@ -3582,14 +3615,11 @@
       <c r="D108" t="s">
         <v>38</v>
       </c>
-      <c r="E108" t="s">
-        <v>98</v>
-      </c>
       <c r="H108" t="s">
         <v>15</v>
       </c>
     </row>
-    <row r="109" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="109" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
       <c r="A109" t="s">
         <v>9</v>
       </c>
@@ -3602,14 +3632,11 @@
       <c r="D109" t="s">
         <v>38</v>
       </c>
-      <c r="E109" t="s">
-        <v>98</v>
-      </c>
       <c r="H109" t="s">
         <v>15</v>
       </c>
     </row>
-    <row r="110" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="110" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
       <c r="A110" t="s">
         <v>9</v>
       </c>
@@ -3619,14 +3646,14 @@
       <c r="C110" s="1">
         <v>46141</v>
       </c>
-      <c r="E110" t="s">
+      <c r="D110" t="s">
         <v>38</v>
       </c>
       <c r="H110" t="s">
         <v>15</v>
       </c>
     </row>
-    <row r="111" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="111" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
       <c r="A111" t="s">
         <v>9</v>
       </c>
@@ -3643,7 +3670,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="112" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="112" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
       <c r="A112" t="s">
         <v>9</v>
       </c>
@@ -3653,14 +3680,17 @@
       <c r="C112" s="1">
         <v>46143</v>
       </c>
+      <c r="D112" t="s">
+        <v>111</v>
+      </c>
       <c r="E112" t="s">
-        <v>38</v>
+        <v>111</v>
       </c>
       <c r="H112" t="s">
-        <v>101</v>
-      </c>
-    </row>
-    <row r="113" spans="1:8" x14ac:dyDescent="0.35">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="113" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
       <c r="A113" t="s">
         <v>9</v>
       </c>
@@ -3677,7 +3707,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="114" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="114" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
       <c r="A114" t="s">
         <v>9</v>
       </c>
@@ -3694,7 +3724,7 @@
         <v>63</v>
       </c>
     </row>
-    <row r="115" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="115" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
       <c r="A115" t="s">
         <v>9</v>
       </c>
@@ -3704,11 +3734,14 @@
       <c r="C115" s="1">
         <v>46148</v>
       </c>
+      <c r="E115" t="s">
+        <v>38</v>
+      </c>
       <c r="H115" t="s">
         <v>15</v>
       </c>
     </row>
-    <row r="116" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="116" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
       <c r="A116" t="s">
         <v>9</v>
       </c>
@@ -3718,11 +3751,14 @@
       <c r="C116" s="1">
         <v>46149</v>
       </c>
+      <c r="E116" t="s">
+        <v>38</v>
+      </c>
       <c r="H116" t="s">
         <v>15</v>
       </c>
     </row>
-    <row r="117" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="117" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
       <c r="A117" t="s">
         <v>9</v>
       </c>
@@ -3732,11 +3768,17 @@
       <c r="C117" s="1">
         <v>46150</v>
       </c>
+      <c r="D117" t="s">
+        <v>111</v>
+      </c>
+      <c r="E117" t="s">
+        <v>111</v>
+      </c>
       <c r="H117" t="s">
-        <v>102</v>
-      </c>
-    </row>
-    <row r="118" spans="1:8" x14ac:dyDescent="0.35">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="118" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
       <c r="A118" t="s">
         <v>9</v>
       </c>
@@ -3750,7 +3792,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="119" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="119" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
       <c r="A119" t="s">
         <v>9</v>
       </c>
@@ -3764,7 +3806,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="120" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="120" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
       <c r="A120" t="s">
         <v>9</v>
       </c>
@@ -3778,7 +3820,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="121" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="121" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
       <c r="A121" t="s">
         <v>9</v>
       </c>
@@ -3792,7 +3834,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="122" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="122" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
       <c r="A122" t="s">
         <v>9</v>
       </c>
@@ -3802,11 +3844,17 @@
       <c r="C122" s="1">
         <v>46157</v>
       </c>
+      <c r="D122" t="s">
+        <v>111</v>
+      </c>
+      <c r="E122" t="s">
+        <v>111</v>
+      </c>
       <c r="H122" t="s">
         <v>15</v>
       </c>
     </row>
-    <row r="123" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="123" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
       <c r="A123" t="s">
         <v>9</v>
       </c>
@@ -3820,7 +3868,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="124" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="124" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
       <c r="A124" t="s">
         <v>9</v>
       </c>
@@ -3834,7 +3882,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="125" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="125" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
       <c r="A125" t="s">
         <v>9</v>
       </c>
@@ -3848,7 +3896,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="126" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="126" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
       <c r="A126" t="s">
         <v>9</v>
       </c>
@@ -3862,7 +3910,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="127" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="127" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
       <c r="A127" t="s">
         <v>9</v>
       </c>
@@ -3885,7 +3933,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="128" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="128" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
       <c r="A128" t="s">
         <v>9</v>
       </c>
@@ -3908,7 +3956,7 @@
         <v>72</v>
       </c>
     </row>
-    <row r="129" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="129" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
       <c r="A129" t="s">
         <v>9</v>
       </c>
@@ -3922,7 +3970,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="130" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="130" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
       <c r="A130" t="s">
         <v>9</v>
       </c>
@@ -3936,7 +3984,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="131" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="131" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
       <c r="A131" t="s">
         <v>9</v>
       </c>
@@ -3950,7 +3998,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="132" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="132" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
       <c r="A132" t="s">
         <v>9</v>
       </c>
@@ -3961,10 +4009,10 @@
         <v>46171</v>
       </c>
       <c r="H132" t="s">
-        <v>102</v>
-      </c>
-    </row>
-    <row r="133" spans="1:8" x14ac:dyDescent="0.35">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="133" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
       <c r="A133" t="s">
         <v>9</v>
       </c>
@@ -3978,7 +4026,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="134" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="134" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
       <c r="A134" t="s">
         <v>9</v>
       </c>
@@ -3992,7 +4040,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="135" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="135" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
       <c r="A135" t="s">
         <v>9</v>
       </c>
@@ -4006,7 +4054,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="136" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="136" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
       <c r="A136" t="s">
         <v>9</v>
       </c>
@@ -4020,7 +4068,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="137" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="137" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
       <c r="A137" t="s">
         <v>9</v>
       </c>
@@ -4031,10 +4079,10 @@
         <v>46178</v>
       </c>
       <c r="H137" t="s">
-        <v>103</v>
-      </c>
-    </row>
-    <row r="138" spans="1:8" x14ac:dyDescent="0.35">
+        <v>102</v>
+      </c>
+    </row>
+    <row r="138" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
       <c r="A138" t="s">
         <v>9</v>
       </c>
@@ -4048,7 +4096,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="139" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="139" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
       <c r="A139" t="s">
         <v>9</v>
       </c>
@@ -4062,16 +4110,19 @@
         <v>15</v>
       </c>
     </row>
-    <row r="140" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="140" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
       <c r="A140" t="s">
         <v>9</v>
       </c>
       <c r="B140" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="C140" s="1">
         <v>46086</v>
       </c>
+      <c r="D140" s="3" t="s">
+        <v>112</v>
+      </c>
       <c r="F140" t="s">
         <v>76</v>
       </c>
@@ -4079,16 +4130,19 @@
         <v>12</v>
       </c>
     </row>
-    <row r="141" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="141" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
       <c r="A141" t="s">
         <v>9</v>
       </c>
       <c r="B141" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="C141" s="1">
         <v>46087</v>
       </c>
+      <c r="D141" t="s">
+        <v>113</v>
+      </c>
       <c r="F141" t="s">
         <v>76</v>
       </c>
@@ -4096,16 +4150,19 @@
         <v>12</v>
       </c>
     </row>
-    <row r="142" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="142" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
       <c r="A142" t="s">
         <v>9</v>
       </c>
       <c r="B142" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="C142" s="1">
         <v>46090</v>
       </c>
+      <c r="D142" t="s">
+        <v>14</v>
+      </c>
       <c r="F142" t="s">
         <v>76</v>
       </c>
@@ -4113,42 +4170,42 @@
         <v>15</v>
       </c>
     </row>
-    <row r="143" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="143" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
       <c r="A143" t="s">
         <v>9</v>
       </c>
       <c r="B143" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="C143" s="1">
         <v>46091</v>
       </c>
       <c r="D143" t="s">
-        <v>100</v>
-      </c>
-      <c r="E143" t="s">
-        <v>100</v>
+        <v>114</v>
       </c>
       <c r="F143" t="s">
         <v>76</v>
       </c>
       <c r="G143" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="H143" t="s">
         <v>17</v>
       </c>
     </row>
-    <row r="144" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="144" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
       <c r="A144" t="s">
         <v>9</v>
       </c>
       <c r="B144" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="C144" s="1">
         <v>46092</v>
       </c>
+      <c r="D144" t="s">
+        <v>86</v>
+      </c>
       <c r="F144" t="s">
         <v>76</v>
       </c>
@@ -4156,16 +4213,19 @@
         <v>15</v>
       </c>
     </row>
-    <row r="145" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="145" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
       <c r="A145" t="s">
         <v>9</v>
       </c>
       <c r="B145" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="C145" s="1">
         <v>46093</v>
       </c>
+      <c r="D145" t="s">
+        <v>115</v>
+      </c>
       <c r="F145" t="s">
         <v>76</v>
       </c>
@@ -4173,16 +4233,19 @@
         <v>15</v>
       </c>
     </row>
-    <row r="146" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="146" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
       <c r="A146" t="s">
         <v>9</v>
       </c>
       <c r="B146" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="C146" s="1">
         <v>46094</v>
       </c>
+      <c r="D146" t="s">
+        <v>116</v>
+      </c>
       <c r="F146" t="s">
         <v>85</v>
       </c>
@@ -4190,16 +4253,19 @@
         <v>22</v>
       </c>
     </row>
-    <row r="147" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="147" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
       <c r="A147" t="s">
         <v>9</v>
       </c>
       <c r="B147" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="C147" s="1">
         <v>46097</v>
       </c>
+      <c r="D147" t="s">
+        <v>117</v>
+      </c>
       <c r="F147" t="s">
         <v>87</v>
       </c>
@@ -4207,16 +4273,19 @@
         <v>25</v>
       </c>
     </row>
-    <row r="148" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="148" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
       <c r="A148" t="s">
         <v>9</v>
       </c>
       <c r="B148" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="C148" s="1">
         <v>46098</v>
       </c>
+      <c r="D148" t="s">
+        <v>118</v>
+      </c>
       <c r="F148" t="s">
         <v>87</v>
       </c>
@@ -4224,16 +4293,19 @@
         <v>25</v>
       </c>
     </row>
-    <row r="149" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="149" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
       <c r="A149" t="s">
         <v>9</v>
       </c>
       <c r="B149" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="C149" s="1">
         <v>46099</v>
       </c>
+      <c r="D149" t="s">
+        <v>119</v>
+      </c>
       <c r="F149" t="s">
         <v>87</v>
       </c>
@@ -4241,12 +4313,12 @@
         <v>29</v>
       </c>
     </row>
-    <row r="150" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="150" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
       <c r="A150" t="s">
         <v>9</v>
       </c>
       <c r="B150" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="C150" s="1">
         <v>46100</v>
@@ -4258,12 +4330,12 @@
         <v>25</v>
       </c>
     </row>
-    <row r="151" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="151" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
       <c r="A151" t="s">
         <v>9</v>
       </c>
       <c r="B151" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="C151" s="1">
         <v>46101</v>
@@ -4275,12 +4347,12 @@
         <v>25</v>
       </c>
     </row>
-    <row r="152" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="152" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
       <c r="A152" t="s">
         <v>9</v>
       </c>
       <c r="B152" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="C152" s="1">
         <v>46104</v>
@@ -4292,12 +4364,12 @@
         <v>17</v>
       </c>
     </row>
-    <row r="153" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="153" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
       <c r="A153" t="s">
         <v>9</v>
       </c>
       <c r="B153" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="C153" s="1">
         <v>46105</v>
@@ -4309,12 +4381,12 @@
         <v>32</v>
       </c>
     </row>
-    <row r="154" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="154" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
       <c r="A154" t="s">
         <v>9</v>
       </c>
       <c r="B154" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="C154" s="1">
         <v>46106</v>
@@ -4326,12 +4398,12 @@
         <v>15</v>
       </c>
     </row>
-    <row r="155" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="155" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
       <c r="A155" t="s">
         <v>9</v>
       </c>
       <c r="B155" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="C155" s="1">
         <v>46107</v>
@@ -4343,30 +4415,39 @@
         <v>15</v>
       </c>
     </row>
-    <row r="156" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="156" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
       <c r="A156" t="s">
         <v>9</v>
       </c>
       <c r="B156" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="C156" s="1">
         <v>46108</v>
       </c>
+      <c r="F156" t="s">
+        <v>93</v>
+      </c>
       <c r="H156" t="s">
         <v>34</v>
       </c>
     </row>
-    <row r="157" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="157" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
       <c r="A157" t="s">
         <v>9</v>
       </c>
       <c r="B157" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="C157" s="1">
         <v>46111</v>
       </c>
+      <c r="D157" t="s">
+        <v>35</v>
+      </c>
+      <c r="F157" t="s">
+        <v>35</v>
+      </c>
       <c r="G157" t="s">
         <v>36</v>
       </c>
@@ -4374,16 +4455,22 @@
         <v>37</v>
       </c>
     </row>
-    <row r="158" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="158" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
       <c r="A158" t="s">
         <v>9</v>
       </c>
       <c r="B158" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="C158" s="1">
         <v>46112</v>
       </c>
+      <c r="D158" t="s">
+        <v>35</v>
+      </c>
+      <c r="F158" t="s">
+        <v>35</v>
+      </c>
       <c r="G158" t="s">
         <v>36</v>
       </c>
@@ -4391,16 +4478,22 @@
         <v>37</v>
       </c>
     </row>
-    <row r="159" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="159" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
       <c r="A159" t="s">
         <v>9</v>
       </c>
       <c r="B159" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="C159" s="1">
         <v>46113</v>
       </c>
+      <c r="D159" t="s">
+        <v>35</v>
+      </c>
+      <c r="F159" t="s">
+        <v>35</v>
+      </c>
       <c r="G159" t="s">
         <v>36</v>
       </c>
@@ -4408,16 +4501,22 @@
         <v>37</v>
       </c>
     </row>
-    <row r="160" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="160" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
       <c r="A160" t="s">
         <v>9</v>
       </c>
       <c r="B160" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="C160" s="1">
         <v>46114</v>
       </c>
+      <c r="D160" t="s">
+        <v>35</v>
+      </c>
+      <c r="F160" t="s">
+        <v>35</v>
+      </c>
       <c r="G160" t="s">
         <v>36</v>
       </c>
@@ -4425,16 +4524,22 @@
         <v>37</v>
       </c>
     </row>
-    <row r="161" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="161" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
       <c r="A161" t="s">
         <v>9</v>
       </c>
       <c r="B161" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="C161" s="1">
         <v>46115</v>
       </c>
+      <c r="D161" t="s">
+        <v>35</v>
+      </c>
+      <c r="F161" t="s">
+        <v>35</v>
+      </c>
       <c r="G161" t="s">
         <v>36</v>
       </c>
@@ -4442,12 +4547,12 @@
         <v>37</v>
       </c>
     </row>
-    <row r="162" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="162" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
       <c r="A162" t="s">
         <v>9</v>
       </c>
       <c r="B162" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="C162" s="1">
         <v>46118</v>
@@ -4456,12 +4561,12 @@
         <v>40</v>
       </c>
     </row>
-    <row r="163" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="163" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
       <c r="A163" t="s">
         <v>9</v>
       </c>
       <c r="B163" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="C163" s="1">
         <v>46119</v>
@@ -4470,12 +4575,12 @@
         <v>15</v>
       </c>
     </row>
-    <row r="164" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="164" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
       <c r="A164" t="s">
         <v>9</v>
       </c>
       <c r="B164" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="C164" s="1">
         <v>46120</v>
@@ -4484,12 +4589,12 @@
         <v>43</v>
       </c>
     </row>
-    <row r="165" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="165" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
       <c r="A165" t="s">
         <v>9</v>
       </c>
       <c r="B165" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="C165" s="1">
         <v>46121</v>
@@ -4498,12 +4603,12 @@
         <v>15</v>
       </c>
     </row>
-    <row r="166" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="166" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
       <c r="A166" t="s">
         <v>9</v>
       </c>
       <c r="B166" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="C166" s="1">
         <v>46122</v>
@@ -4512,12 +4617,12 @@
         <v>15</v>
       </c>
     </row>
-    <row r="167" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="167" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
       <c r="A167" t="s">
         <v>9</v>
       </c>
       <c r="B167" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="C167" s="1">
         <v>46125</v>
@@ -4526,12 +4631,12 @@
         <v>15</v>
       </c>
     </row>
-    <row r="168" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="168" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
       <c r="A168" t="s">
         <v>9</v>
       </c>
       <c r="B168" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="C168" s="1">
         <v>46126</v>
@@ -4540,12 +4645,12 @@
         <v>15</v>
       </c>
     </row>
-    <row r="169" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="169" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
       <c r="A169" t="s">
         <v>9</v>
       </c>
       <c r="B169" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="C169" s="1">
         <v>46127</v>
@@ -4554,16 +4659,19 @@
         <v>15</v>
       </c>
     </row>
-    <row r="170" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="170" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
       <c r="A170" t="s">
         <v>9</v>
       </c>
       <c r="B170" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="C170" s="1">
         <v>46128</v>
       </c>
+      <c r="D170" t="s">
+        <v>46</v>
+      </c>
       <c r="G170" t="s">
         <v>47</v>
       </c>
@@ -4571,16 +4679,19 @@
         <v>15</v>
       </c>
     </row>
-    <row r="171" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="171" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
       <c r="A171" t="s">
         <v>9</v>
       </c>
       <c r="B171" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="C171" s="1">
         <v>46129</v>
       </c>
+      <c r="D171" t="s">
+        <v>98</v>
+      </c>
       <c r="G171" t="s">
         <v>49</v>
       </c>
@@ -4588,12 +4699,12 @@
         <v>50</v>
       </c>
     </row>
-    <row r="172" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="172" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
       <c r="A172" t="s">
         <v>9</v>
       </c>
       <c r="B172" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="C172" s="1">
         <v>46132</v>
@@ -4602,32 +4713,26 @@
         <v>15</v>
       </c>
     </row>
-    <row r="173" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="173" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
       <c r="A173" t="s">
         <v>9</v>
       </c>
       <c r="B173" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="C173" s="1">
         <v>46133</v>
       </c>
-      <c r="E173" t="s">
-        <v>100</v>
-      </c>
-      <c r="G173" t="s">
-        <v>106</v>
-      </c>
       <c r="H173" t="s">
         <v>15</v>
       </c>
     </row>
-    <row r="174" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="174" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
       <c r="A174" t="s">
         <v>9</v>
       </c>
       <c r="B174" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="C174" s="1">
         <v>46134</v>
@@ -4636,12 +4741,12 @@
         <v>15</v>
       </c>
     </row>
-    <row r="175" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="175" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
       <c r="A175" t="s">
         <v>9</v>
       </c>
       <c r="B175" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="C175" s="1">
         <v>46135</v>
@@ -4650,12 +4755,12 @@
         <v>15</v>
       </c>
     </row>
-    <row r="176" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="176" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
       <c r="A176" t="s">
         <v>9</v>
       </c>
       <c r="B176" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="C176" s="1">
         <v>46136</v>
@@ -4664,12 +4769,12 @@
         <v>15</v>
       </c>
     </row>
-    <row r="177" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="177" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
       <c r="A177" t="s">
         <v>9</v>
       </c>
       <c r="B177" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="C177" s="1">
         <v>46139</v>
@@ -4678,12 +4783,12 @@
         <v>15</v>
       </c>
     </row>
-    <row r="178" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="178" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
       <c r="A178" t="s">
         <v>9</v>
       </c>
       <c r="B178" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="C178" s="1">
         <v>46140</v>
@@ -4692,12 +4797,12 @@
         <v>15</v>
       </c>
     </row>
-    <row r="179" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="179" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
       <c r="A179" t="s">
         <v>9</v>
       </c>
       <c r="B179" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="C179" s="1">
         <v>46141</v>
@@ -4706,12 +4811,12 @@
         <v>15</v>
       </c>
     </row>
-    <row r="180" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="180" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
       <c r="A180" t="s">
         <v>9</v>
       </c>
       <c r="B180" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="C180" s="1">
         <v>46142</v>
@@ -4720,26 +4825,26 @@
         <v>15</v>
       </c>
     </row>
-    <row r="181" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="181" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
       <c r="A181" t="s">
         <v>9</v>
       </c>
       <c r="B181" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="C181" s="1">
         <v>46143</v>
       </c>
       <c r="H181" t="s">
-        <v>101</v>
-      </c>
-    </row>
-    <row r="182" spans="1:8" x14ac:dyDescent="0.35">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="182" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
       <c r="A182" t="s">
         <v>9</v>
       </c>
       <c r="B182" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="C182" s="1">
         <v>46146</v>
@@ -4748,12 +4853,12 @@
         <v>15</v>
       </c>
     </row>
-    <row r="183" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="183" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
       <c r="A183" t="s">
         <v>9</v>
       </c>
       <c r="B183" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="C183" s="1">
         <v>46147</v>
@@ -4762,12 +4867,12 @@
         <v>63</v>
       </c>
     </row>
-    <row r="184" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="184" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
       <c r="A184" t="s">
         <v>9</v>
       </c>
       <c r="B184" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="C184" s="1">
         <v>46148</v>
@@ -4776,12 +4881,12 @@
         <v>15</v>
       </c>
     </row>
-    <row r="185" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="185" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
       <c r="A185" t="s">
         <v>9</v>
       </c>
       <c r="B185" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="C185" s="1">
         <v>46149</v>
@@ -4790,26 +4895,26 @@
         <v>15</v>
       </c>
     </row>
-    <row r="186" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="186" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
       <c r="A186" t="s">
         <v>9</v>
       </c>
       <c r="B186" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="C186" s="1">
         <v>46150</v>
       </c>
       <c r="H186" t="s">
-        <v>102</v>
-      </c>
-    </row>
-    <row r="187" spans="1:8" x14ac:dyDescent="0.35">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="187" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
       <c r="A187" t="s">
         <v>9</v>
       </c>
       <c r="B187" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="C187" s="1">
         <v>46153</v>
@@ -4818,12 +4923,12 @@
         <v>15</v>
       </c>
     </row>
-    <row r="188" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="188" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
       <c r="A188" t="s">
         <v>9</v>
       </c>
       <c r="B188" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="C188" s="1">
         <v>46154</v>
@@ -4832,12 +4937,12 @@
         <v>15</v>
       </c>
     </row>
-    <row r="189" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="189" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
       <c r="A189" t="s">
         <v>9</v>
       </c>
       <c r="B189" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="C189" s="1">
         <v>46155</v>
@@ -4846,12 +4951,12 @@
         <v>15</v>
       </c>
     </row>
-    <row r="190" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="190" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
       <c r="A190" t="s">
         <v>9</v>
       </c>
       <c r="B190" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="C190" s="1">
         <v>46156</v>
@@ -4860,12 +4965,12 @@
         <v>15</v>
       </c>
     </row>
-    <row r="191" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="191" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
       <c r="A191" t="s">
         <v>9</v>
       </c>
       <c r="B191" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="C191" s="1">
         <v>46157</v>
@@ -4874,12 +4979,12 @@
         <v>15</v>
       </c>
     </row>
-    <row r="192" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="192" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
       <c r="A192" t="s">
         <v>9</v>
       </c>
       <c r="B192" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="C192" s="1">
         <v>46160</v>
@@ -4888,12 +4993,12 @@
         <v>15</v>
       </c>
     </row>
-    <row r="193" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="193" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
       <c r="A193" t="s">
         <v>9</v>
       </c>
       <c r="B193" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="C193" s="1">
         <v>46161</v>
@@ -4902,12 +5007,12 @@
         <v>15</v>
       </c>
     </row>
-    <row r="194" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="194" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
       <c r="A194" t="s">
         <v>9</v>
       </c>
       <c r="B194" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="C194" s="1">
         <v>46162</v>
@@ -4916,12 +5021,12 @@
         <v>15</v>
       </c>
     </row>
-    <row r="195" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="195" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
       <c r="A195" t="s">
         <v>9</v>
       </c>
       <c r="B195" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="C195" s="1">
         <v>46163</v>
@@ -4930,16 +5035,19 @@
         <v>15</v>
       </c>
     </row>
-    <row r="196" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="196" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
       <c r="A196" t="s">
         <v>9</v>
       </c>
       <c r="B196" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="C196" s="1">
         <v>46164</v>
       </c>
+      <c r="D196" t="s">
+        <v>46</v>
+      </c>
       <c r="G196" t="s">
         <v>70</v>
       </c>
@@ -4947,16 +5055,19 @@
         <v>15</v>
       </c>
     </row>
-    <row r="197" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="197" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
       <c r="A197" t="s">
         <v>9</v>
       </c>
       <c r="B197" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="C197" s="1">
         <v>46167</v>
       </c>
+      <c r="D197" t="s">
+        <v>46</v>
+      </c>
       <c r="G197" t="s">
         <v>71</v>
       </c>
@@ -4964,12 +5075,12 @@
         <v>72</v>
       </c>
     </row>
-    <row r="198" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="198" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
       <c r="A198" t="s">
         <v>9</v>
       </c>
       <c r="B198" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="C198" s="1">
         <v>46168</v>
@@ -4978,12 +5089,12 @@
         <v>15</v>
       </c>
     </row>
-    <row r="199" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="199" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
       <c r="A199" t="s">
         <v>9</v>
       </c>
       <c r="B199" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="C199" s="1">
         <v>46169</v>
@@ -4992,12 +5103,12 @@
         <v>15</v>
       </c>
     </row>
-    <row r="200" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="200" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
       <c r="A200" t="s">
         <v>9</v>
       </c>
       <c r="B200" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="C200" s="1">
         <v>46170</v>
@@ -5006,26 +5117,26 @@
         <v>15</v>
       </c>
     </row>
-    <row r="201" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="201" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
       <c r="A201" t="s">
         <v>9</v>
       </c>
       <c r="B201" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="C201" s="1">
         <v>46171</v>
       </c>
       <c r="H201" t="s">
-        <v>102</v>
-      </c>
-    </row>
-    <row r="202" spans="1:8" x14ac:dyDescent="0.35">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="202" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
       <c r="A202" t="s">
         <v>9</v>
       </c>
       <c r="B202" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="C202" s="1">
         <v>46174</v>
@@ -5034,12 +5145,12 @@
         <v>15</v>
       </c>
     </row>
-    <row r="203" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="203" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
       <c r="A203" t="s">
         <v>9</v>
       </c>
       <c r="B203" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="C203" s="1">
         <v>46175</v>
@@ -5048,12 +5159,12 @@
         <v>15</v>
       </c>
     </row>
-    <row r="204" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="204" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
       <c r="A204" t="s">
         <v>9</v>
       </c>
       <c r="B204" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="C204" s="1">
         <v>46176</v>
@@ -5062,12 +5173,12 @@
         <v>15</v>
       </c>
     </row>
-    <row r="205" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="205" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
       <c r="A205" t="s">
         <v>9</v>
       </c>
       <c r="B205" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="C205" s="1">
         <v>46177</v>
@@ -5076,26 +5187,26 @@
         <v>15</v>
       </c>
     </row>
-    <row r="206" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="206" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
       <c r="A206" t="s">
         <v>9</v>
       </c>
       <c r="B206" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="C206" s="1">
         <v>46178</v>
       </c>
       <c r="H206" t="s">
-        <v>103</v>
-      </c>
-    </row>
-    <row r="207" spans="1:8" x14ac:dyDescent="0.35">
+        <v>102</v>
+      </c>
+    </row>
+    <row r="207" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
       <c r="A207" t="s">
         <v>9</v>
       </c>
       <c r="B207" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="C207" s="1">
         <v>46181</v>
@@ -5104,12 +5215,12 @@
         <v>15</v>
       </c>
     </row>
-    <row r="208" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="208" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
       <c r="A208" t="s">
         <v>9</v>
       </c>
       <c r="B208" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="C208" s="1">
         <v>46182</v>
@@ -5123,7 +5234,7 @@
         <v>9</v>
       </c>
       <c r="B209" t="s">
-        <v>107</v>
+        <v>105</v>
       </c>
       <c r="C209" s="1">
         <v>46086</v>
@@ -5140,7 +5251,7 @@
         <v>9</v>
       </c>
       <c r="B210" t="s">
-        <v>107</v>
+        <v>105</v>
       </c>
       <c r="C210" s="1">
         <v>46087</v>
@@ -5157,11 +5268,14 @@
         <v>9</v>
       </c>
       <c r="B211" t="s">
-        <v>107</v>
+        <v>105</v>
       </c>
       <c r="C211" s="1">
         <v>46090</v>
       </c>
+      <c r="D211" t="s">
+        <v>14</v>
+      </c>
       <c r="F211" t="s">
         <v>76</v>
       </c>
@@ -5174,20 +5288,17 @@
         <v>9</v>
       </c>
       <c r="B212" t="s">
-        <v>107</v>
+        <v>105</v>
       </c>
       <c r="C212" s="1">
         <v>46091</v>
       </c>
       <c r="D212" t="s">
-        <v>100</v>
+        <v>120</v>
       </c>
       <c r="F212" t="s">
         <v>76</v>
       </c>
-      <c r="G212" t="s">
-        <v>108</v>
-      </c>
       <c r="H212" t="s">
         <v>17</v>
       </c>
@@ -5197,7 +5308,7 @@
         <v>9</v>
       </c>
       <c r="B213" t="s">
-        <v>107</v>
+        <v>105</v>
       </c>
       <c r="C213" s="1">
         <v>46092</v>
@@ -5214,7 +5325,7 @@
         <v>9</v>
       </c>
       <c r="B214" t="s">
-        <v>107</v>
+        <v>105</v>
       </c>
       <c r="C214" s="1">
         <v>46093</v>
@@ -5226,27 +5337,24 @@
         <v>15</v>
       </c>
     </row>
-    <row r="215" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="215" spans="1:8" ht="29" x14ac:dyDescent="0.35">
       <c r="A215" t="s">
         <v>9</v>
       </c>
       <c r="B215" t="s">
-        <v>107</v>
+        <v>105</v>
       </c>
       <c r="C215" s="1">
         <v>46094</v>
       </c>
-      <c r="D215" t="s">
-        <v>109</v>
-      </c>
-      <c r="E215" t="s">
-        <v>109</v>
+      <c r="D215" s="2" t="s">
+        <v>123</v>
       </c>
       <c r="F215" t="s">
         <v>85</v>
       </c>
       <c r="G215" t="s">
-        <v>110</v>
+        <v>106</v>
       </c>
       <c r="H215" t="s">
         <v>22</v>
@@ -5257,7 +5365,7 @@
         <v>9</v>
       </c>
       <c r="B216" t="s">
-        <v>107</v>
+        <v>105</v>
       </c>
       <c r="C216" s="1">
         <v>46097</v>
@@ -5274,7 +5382,7 @@
         <v>9</v>
       </c>
       <c r="B217" t="s">
-        <v>107</v>
+        <v>105</v>
       </c>
       <c r="C217" s="1">
         <v>46098</v>
@@ -5291,7 +5399,7 @@
         <v>9</v>
       </c>
       <c r="B218" t="s">
-        <v>107</v>
+        <v>105</v>
       </c>
       <c r="C218" s="1">
         <v>46099</v>
@@ -5300,7 +5408,7 @@
         <v>87</v>
       </c>
       <c r="G218" t="s">
-        <v>114</v>
+        <v>109</v>
       </c>
       <c r="H218" t="s">
         <v>29</v>
@@ -5311,7 +5419,7 @@
         <v>9</v>
       </c>
       <c r="B219" t="s">
-        <v>107</v>
+        <v>105</v>
       </c>
       <c r="C219" s="1">
         <v>46100</v>
@@ -5328,22 +5436,19 @@
         <v>9</v>
       </c>
       <c r="B220" t="s">
-        <v>107</v>
+        <v>105</v>
       </c>
       <c r="C220" s="1">
         <v>46101</v>
       </c>
       <c r="D220" t="s">
-        <v>112</v>
-      </c>
-      <c r="E220" t="s">
-        <v>112</v>
+        <v>124</v>
       </c>
       <c r="F220" t="s">
         <v>91</v>
       </c>
       <c r="G220" t="s">
-        <v>111</v>
+        <v>107</v>
       </c>
       <c r="H220" t="s">
         <v>25</v>
@@ -5354,7 +5459,7 @@
         <v>9</v>
       </c>
       <c r="B221" t="s">
-        <v>107</v>
+        <v>105</v>
       </c>
       <c r="C221" s="1">
         <v>46104</v>
@@ -5368,7 +5473,7 @@
         <v>9</v>
       </c>
       <c r="B222" t="s">
-        <v>107</v>
+        <v>105</v>
       </c>
       <c r="C222" s="1">
         <v>46105</v>
@@ -5382,7 +5487,7 @@
         <v>9</v>
       </c>
       <c r="B223" t="s">
-        <v>107</v>
+        <v>105</v>
       </c>
       <c r="C223" s="1">
         <v>46106</v>
@@ -5396,7 +5501,7 @@
         <v>9</v>
       </c>
       <c r="B224" t="s">
-        <v>107</v>
+        <v>105</v>
       </c>
       <c r="C224" s="1">
         <v>46107</v>
@@ -5410,11 +5515,14 @@
         <v>9</v>
       </c>
       <c r="B225" t="s">
-        <v>107</v>
+        <v>105</v>
       </c>
       <c r="C225" s="1">
         <v>46108</v>
       </c>
+      <c r="D225" t="s">
+        <v>124</v>
+      </c>
       <c r="H225" t="s">
         <v>34</v>
       </c>
@@ -5424,11 +5532,17 @@
         <v>9</v>
       </c>
       <c r="B226" t="s">
-        <v>107</v>
+        <v>105</v>
       </c>
       <c r="C226" s="1">
         <v>46111</v>
       </c>
+      <c r="D226" t="s">
+        <v>35</v>
+      </c>
+      <c r="F226" t="s">
+        <v>35</v>
+      </c>
       <c r="G226" t="s">
         <v>36</v>
       </c>
@@ -5441,11 +5555,17 @@
         <v>9</v>
       </c>
       <c r="B227" t="s">
-        <v>107</v>
+        <v>105</v>
       </c>
       <c r="C227" s="1">
         <v>46112</v>
       </c>
+      <c r="D227" t="s">
+        <v>35</v>
+      </c>
+      <c r="F227" t="s">
+        <v>35</v>
+      </c>
       <c r="G227" t="s">
         <v>36</v>
       </c>
@@ -5458,11 +5578,17 @@
         <v>9</v>
       </c>
       <c r="B228" t="s">
-        <v>107</v>
+        <v>105</v>
       </c>
       <c r="C228" s="1">
         <v>46113</v>
       </c>
+      <c r="D228" t="s">
+        <v>35</v>
+      </c>
+      <c r="F228" t="s">
+        <v>35</v>
+      </c>
       <c r="G228" t="s">
         <v>36</v>
       </c>
@@ -5475,11 +5601,17 @@
         <v>9</v>
       </c>
       <c r="B229" t="s">
-        <v>107</v>
+        <v>105</v>
       </c>
       <c r="C229" s="1">
         <v>46114</v>
       </c>
+      <c r="D229" t="s">
+        <v>35</v>
+      </c>
+      <c r="F229" t="s">
+        <v>35</v>
+      </c>
       <c r="G229" t="s">
         <v>36</v>
       </c>
@@ -5492,11 +5624,17 @@
         <v>9</v>
       </c>
       <c r="B230" t="s">
-        <v>107</v>
+        <v>105</v>
       </c>
       <c r="C230" s="1">
         <v>46115</v>
       </c>
+      <c r="D230" t="s">
+        <v>35</v>
+      </c>
+      <c r="F230" t="s">
+        <v>35</v>
+      </c>
       <c r="G230" t="s">
         <v>36</v>
       </c>
@@ -5509,7 +5647,7 @@
         <v>9</v>
       </c>
       <c r="B231" t="s">
-        <v>107</v>
+        <v>105</v>
       </c>
       <c r="C231" s="1">
         <v>46118</v>
@@ -5523,7 +5661,7 @@
         <v>9</v>
       </c>
       <c r="B232" t="s">
-        <v>107</v>
+        <v>105</v>
       </c>
       <c r="C232" s="1">
         <v>46119</v>
@@ -5537,7 +5675,7 @@
         <v>9</v>
       </c>
       <c r="B233" t="s">
-        <v>107</v>
+        <v>105</v>
       </c>
       <c r="C233" s="1">
         <v>46120</v>
@@ -5551,7 +5689,7 @@
         <v>9</v>
       </c>
       <c r="B234" t="s">
-        <v>107</v>
+        <v>105</v>
       </c>
       <c r="C234" s="1">
         <v>46121</v>
@@ -5565,11 +5703,14 @@
         <v>9</v>
       </c>
       <c r="B235" t="s">
-        <v>107</v>
+        <v>105</v>
       </c>
       <c r="C235" s="1">
         <v>46122</v>
       </c>
+      <c r="D235" t="s">
+        <v>121</v>
+      </c>
       <c r="H235" t="s">
         <v>15</v>
       </c>
@@ -5579,7 +5720,7 @@
         <v>9</v>
       </c>
       <c r="B236" t="s">
-        <v>107</v>
+        <v>105</v>
       </c>
       <c r="C236" s="1">
         <v>46125</v>
@@ -5593,7 +5734,7 @@
         <v>9</v>
       </c>
       <c r="B237" t="s">
-        <v>107</v>
+        <v>105</v>
       </c>
       <c r="C237" s="1">
         <v>46126</v>
@@ -5607,7 +5748,7 @@
         <v>9</v>
       </c>
       <c r="B238" t="s">
-        <v>107</v>
+        <v>105</v>
       </c>
       <c r="C238" s="1">
         <v>46127</v>
@@ -5621,7 +5762,7 @@
         <v>9</v>
       </c>
       <c r="B239" t="s">
-        <v>107</v>
+        <v>105</v>
       </c>
       <c r="C239" s="1">
         <v>46128</v>
@@ -5629,9 +5770,6 @@
       <c r="D239" t="s">
         <v>46</v>
       </c>
-      <c r="E239" t="s">
-        <v>46</v>
-      </c>
       <c r="G239" t="s">
         <v>47</v>
       </c>
@@ -5644,16 +5782,13 @@
         <v>9</v>
       </c>
       <c r="B240" t="s">
-        <v>107</v>
+        <v>105</v>
       </c>
       <c r="C240" s="1">
         <v>46129</v>
       </c>
       <c r="D240" t="s">
-        <v>99</v>
-      </c>
-      <c r="E240" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="G240" t="s">
         <v>49</v>
@@ -5667,7 +5802,7 @@
         <v>9</v>
       </c>
       <c r="B241" t="s">
-        <v>107</v>
+        <v>105</v>
       </c>
       <c r="C241" s="1">
         <v>46132</v>
@@ -5681,7 +5816,7 @@
         <v>9</v>
       </c>
       <c r="B242" t="s">
-        <v>107</v>
+        <v>105</v>
       </c>
       <c r="C242" s="1">
         <v>46133</v>
@@ -5695,7 +5830,7 @@
         <v>9</v>
       </c>
       <c r="B243" t="s">
-        <v>107</v>
+        <v>105</v>
       </c>
       <c r="C243" s="1">
         <v>46134</v>
@@ -5709,7 +5844,7 @@
         <v>9</v>
       </c>
       <c r="B244" t="s">
-        <v>107</v>
+        <v>105</v>
       </c>
       <c r="C244" s="1">
         <v>46135</v>
@@ -5723,11 +5858,14 @@
         <v>9</v>
       </c>
       <c r="B245" t="s">
-        <v>107</v>
+        <v>105</v>
       </c>
       <c r="C245" s="1">
         <v>46136</v>
       </c>
+      <c r="D245" t="s">
+        <v>122</v>
+      </c>
       <c r="H245" t="s">
         <v>15</v>
       </c>
@@ -5737,11 +5875,14 @@
         <v>9</v>
       </c>
       <c r="B246" t="s">
-        <v>107</v>
+        <v>105</v>
       </c>
       <c r="C246" s="1">
         <v>46139</v>
       </c>
+      <c r="D246" t="s">
+        <v>125</v>
+      </c>
       <c r="H246" t="s">
         <v>15</v>
       </c>
@@ -5751,11 +5892,14 @@
         <v>9</v>
       </c>
       <c r="B247" t="s">
-        <v>107</v>
+        <v>105</v>
       </c>
       <c r="C247" s="1">
         <v>46140</v>
       </c>
+      <c r="D247" t="s">
+        <v>125</v>
+      </c>
       <c r="H247" t="s">
         <v>15</v>
       </c>
@@ -5765,11 +5909,14 @@
         <v>9</v>
       </c>
       <c r="B248" t="s">
-        <v>107</v>
+        <v>105</v>
       </c>
       <c r="C248" s="1">
         <v>46141</v>
       </c>
+      <c r="D248" t="s">
+        <v>125</v>
+      </c>
       <c r="H248" t="s">
         <v>15</v>
       </c>
@@ -5779,11 +5926,14 @@
         <v>9</v>
       </c>
       <c r="B249" t="s">
-        <v>107</v>
+        <v>105</v>
       </c>
       <c r="C249" s="1">
         <v>46142</v>
       </c>
+      <c r="D249" t="s">
+        <v>125</v>
+      </c>
       <c r="H249" t="s">
         <v>15</v>
       </c>
@@ -5793,13 +5943,16 @@
         <v>9</v>
       </c>
       <c r="B250" t="s">
-        <v>107</v>
+        <v>105</v>
       </c>
       <c r="C250" s="1">
         <v>46143</v>
       </c>
+      <c r="D250" t="s">
+        <v>125</v>
+      </c>
       <c r="H250" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
     </row>
     <row r="251" spans="1:8" x14ac:dyDescent="0.35">
@@ -5807,11 +5960,14 @@
         <v>9</v>
       </c>
       <c r="B251" t="s">
-        <v>107</v>
+        <v>105</v>
       </c>
       <c r="C251" s="1">
         <v>46146</v>
       </c>
+      <c r="D251" t="s">
+        <v>125</v>
+      </c>
       <c r="H251" t="s">
         <v>15</v>
       </c>
@@ -5821,11 +5977,14 @@
         <v>9</v>
       </c>
       <c r="B252" t="s">
-        <v>107</v>
+        <v>105</v>
       </c>
       <c r="C252" s="1">
         <v>46147</v>
       </c>
+      <c r="D252" t="s">
+        <v>125</v>
+      </c>
       <c r="H252" t="s">
         <v>63</v>
       </c>
@@ -5835,11 +5994,14 @@
         <v>9</v>
       </c>
       <c r="B253" t="s">
-        <v>107</v>
+        <v>105</v>
       </c>
       <c r="C253" s="1">
         <v>46148</v>
       </c>
+      <c r="D253" t="s">
+        <v>125</v>
+      </c>
       <c r="H253" t="s">
         <v>15</v>
       </c>
@@ -5849,11 +6011,14 @@
         <v>9</v>
       </c>
       <c r="B254" t="s">
-        <v>107</v>
+        <v>105</v>
       </c>
       <c r="C254" s="1">
         <v>46149</v>
       </c>
+      <c r="D254" t="s">
+        <v>125</v>
+      </c>
       <c r="H254" t="s">
         <v>15</v>
       </c>
@@ -5863,13 +6028,16 @@
         <v>9</v>
       </c>
       <c r="B255" t="s">
-        <v>107</v>
+        <v>105</v>
       </c>
       <c r="C255" s="1">
         <v>46150</v>
       </c>
+      <c r="D255" t="s">
+        <v>125</v>
+      </c>
       <c r="H255" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
     </row>
     <row r="256" spans="1:8" x14ac:dyDescent="0.35">
@@ -5877,11 +6045,14 @@
         <v>9</v>
       </c>
       <c r="B256" t="s">
-        <v>107</v>
+        <v>105</v>
       </c>
       <c r="C256" s="1">
         <v>46153</v>
       </c>
+      <c r="D256" t="s">
+        <v>125</v>
+      </c>
       <c r="H256" t="s">
         <v>15</v>
       </c>
@@ -5891,11 +6062,14 @@
         <v>9</v>
       </c>
       <c r="B257" t="s">
-        <v>107</v>
+        <v>105</v>
       </c>
       <c r="C257" s="1">
         <v>46154</v>
       </c>
+      <c r="D257" t="s">
+        <v>125</v>
+      </c>
       <c r="H257" t="s">
         <v>15</v>
       </c>
@@ -5905,11 +6079,14 @@
         <v>9</v>
       </c>
       <c r="B258" t="s">
-        <v>107</v>
+        <v>105</v>
       </c>
       <c r="C258" s="1">
         <v>46155</v>
       </c>
+      <c r="D258" t="s">
+        <v>125</v>
+      </c>
       <c r="H258" t="s">
         <v>15</v>
       </c>
@@ -5919,7 +6096,7 @@
         <v>9</v>
       </c>
       <c r="B259" t="s">
-        <v>107</v>
+        <v>105</v>
       </c>
       <c r="C259" s="1">
         <v>46156</v>
@@ -5933,16 +6110,13 @@
         <v>9</v>
       </c>
       <c r="B260" t="s">
-        <v>107</v>
+        <v>105</v>
       </c>
       <c r="C260" s="1">
         <v>46157</v>
       </c>
       <c r="D260" t="s">
-        <v>113</v>
-      </c>
-      <c r="E260" t="s">
-        <v>113</v>
+        <v>108</v>
       </c>
       <c r="H260" t="s">
         <v>15</v>
@@ -5953,7 +6127,7 @@
         <v>9</v>
       </c>
       <c r="B261" t="s">
-        <v>107</v>
+        <v>105</v>
       </c>
       <c r="C261" s="1">
         <v>46160</v>
@@ -5967,7 +6141,7 @@
         <v>9</v>
       </c>
       <c r="B262" t="s">
-        <v>107</v>
+        <v>105</v>
       </c>
       <c r="C262" s="1">
         <v>46161</v>
@@ -5981,7 +6155,7 @@
         <v>9</v>
       </c>
       <c r="B263" t="s">
-        <v>107</v>
+        <v>105</v>
       </c>
       <c r="C263" s="1">
         <v>46162</v>
@@ -5995,7 +6169,7 @@
         <v>9</v>
       </c>
       <c r="B264" t="s">
-        <v>107</v>
+        <v>105</v>
       </c>
       <c r="C264" s="1">
         <v>46163</v>
@@ -6009,7 +6183,7 @@
         <v>9</v>
       </c>
       <c r="B265" t="s">
-        <v>107</v>
+        <v>105</v>
       </c>
       <c r="C265" s="1">
         <v>46164</v>
@@ -6026,7 +6200,7 @@
         <v>9</v>
       </c>
       <c r="B266" t="s">
-        <v>107</v>
+        <v>105</v>
       </c>
       <c r="C266" s="1">
         <v>46167</v>
@@ -6043,7 +6217,7 @@
         <v>9</v>
       </c>
       <c r="B267" t="s">
-        <v>107</v>
+        <v>105</v>
       </c>
       <c r="C267" s="1">
         <v>46168</v>
@@ -6057,7 +6231,7 @@
         <v>9</v>
       </c>
       <c r="B268" t="s">
-        <v>107</v>
+        <v>105</v>
       </c>
       <c r="C268" s="1">
         <v>46169</v>
@@ -6071,7 +6245,7 @@
         <v>9</v>
       </c>
       <c r="B269" t="s">
-        <v>107</v>
+        <v>105</v>
       </c>
       <c r="C269" s="1">
         <v>46170</v>
@@ -6085,13 +6259,13 @@
         <v>9</v>
       </c>
       <c r="B270" t="s">
-        <v>107</v>
+        <v>105</v>
       </c>
       <c r="C270" s="1">
         <v>46171</v>
       </c>
       <c r="H270" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
     </row>
     <row r="271" spans="1:8" x14ac:dyDescent="0.35">
@@ -6099,7 +6273,7 @@
         <v>9</v>
       </c>
       <c r="B271" t="s">
-        <v>107</v>
+        <v>105</v>
       </c>
       <c r="C271" s="1">
         <v>46174</v>
@@ -6113,7 +6287,7 @@
         <v>9</v>
       </c>
       <c r="B272" t="s">
-        <v>107</v>
+        <v>105</v>
       </c>
       <c r="C272" s="1">
         <v>46175</v>
@@ -6127,7 +6301,7 @@
         <v>9</v>
       </c>
       <c r="B273" t="s">
-        <v>107</v>
+        <v>105</v>
       </c>
       <c r="C273" s="1">
         <v>46176</v>
@@ -6141,7 +6315,7 @@
         <v>9</v>
       </c>
       <c r="B274" t="s">
-        <v>107</v>
+        <v>105</v>
       </c>
       <c r="C274" s="1">
         <v>46177</v>
@@ -6155,13 +6329,13 @@
         <v>9</v>
       </c>
       <c r="B275" t="s">
-        <v>107</v>
+        <v>105</v>
       </c>
       <c r="C275" s="1">
         <v>46178</v>
       </c>
       <c r="H275" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
     </row>
     <row r="276" spans="1:8" x14ac:dyDescent="0.35">
@@ -6169,7 +6343,7 @@
         <v>9</v>
       </c>
       <c r="B276" t="s">
-        <v>107</v>
+        <v>105</v>
       </c>
       <c r="C276" s="1">
         <v>46181</v>
@@ -6183,7 +6357,7 @@
         <v>9</v>
       </c>
       <c r="B277" t="s">
-        <v>107</v>
+        <v>105</v>
       </c>
       <c r="C277" s="1">
         <v>46182</v>
@@ -6193,7 +6367,14 @@
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:I277" xr:uid="{3048F481-4A4B-498D-A291-01B119D1D7C2}"/>
+  <autoFilter ref="A1:I277" xr:uid="{3048F481-4A4B-498D-A291-01B119D1D7C2}">
+    <filterColumn colId="1">
+      <filters>
+        <filter val="AP Computer Science A: Game Design"/>
+      </filters>
+    </filterColumn>
+  </autoFilter>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" r:id="rId1"/>
 </worksheet>
 </file>